--- a/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$734</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$H$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet4'!$A$1:$A$5</definedName>
   </definedNames>
@@ -129,11 +129,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="6" min="1" max="1"/>
@@ -423,22 +423,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>cp</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>MNL-002489</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>MNL-002435</t>
         </is>
@@ -547,779 +547,257 @@
       <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>260929A9FF4P5G</t>
+        </is>
+      </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>260929ABKUSD4M</t>
+        </is>
+      </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>260929AC46E1GX</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>260929AD47N1M5</t>
+        </is>
+      </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>260929AKH7WXDK</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>260929ANT8DV9R</t>
+        </is>
+      </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>260929APRFE6V2</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>260929AQ0RMP53</t>
+        </is>
+      </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>260929ARX29XJD</t>
+        </is>
+      </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>260929ATGE266E</t>
+        </is>
+      </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>260929AUBFYE55</t>
+        </is>
+      </c>
       <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>260929AVBTNRTA</t>
+        </is>
+      </c>
       <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>260929AVPCA0XR</t>
+        </is>
+      </c>
       <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>260929AY8WX88S</t>
+        </is>
+      </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>260929B2M5A197</t>
+        </is>
+      </c>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>260929B8BYGF1K</t>
+        </is>
+      </c>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>260929BHGHSUQ3</t>
+        </is>
+      </c>
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>260930BHUKKSRW</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>260930BPV8TJH5</t>
+        </is>
+      </c>
       <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>260930CAR4FKG3</t>
+        </is>
+      </c>
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>260930CBG0C9UW</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>260930CK8G2PJS</t>
+        </is>
+      </c>
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>260930CKQJKFFU</t>
+        </is>
+      </c>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>260930CMWQB2C5</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>260930CPFHU6GG</t>
+        </is>
+      </c>
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr"/>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr"/>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr"/>
-      <c r="B45" s="5" t="inlineStr"/>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr"/>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr"/>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>26092883AKK1P4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>26092884A6G3PR</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr"/>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>26092884G39KUD</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr"/>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>260928853RSEK8</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr"/>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>26092886W6G53F</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>260928872WK7WP</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>260928879FDWKY</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>260928879RWQ3K</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>26092887FNSSK9</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr"/>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>26092888WJCWVA</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr"/>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>26092889TEHHCP</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr"/>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>2609288BXGS0T1</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr"/>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>2609288CBR6CTP</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr"/>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>2609288CCHXCUX</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr"/>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>2609288CFAJECK</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr"/>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>2609288CQX7AV0</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr"/>
-      <c r="C70" s="5" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>2609288D0NM941</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr"/>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>2609288EAT3M0W</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>2609288EHHN19C</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr"/>
-      <c r="C73" s="5" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>2609288EXASJTA</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr"/>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>2609288J8FSUQ7</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr"/>
-      <c r="C75" s="5" t="inlineStr"/>
-      <c r="D75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>2609288JSCF742</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>2609288M2S5X4U</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr"/>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>2609288M9KK28E</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
-      <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="5" t="inlineStr"/>
-      <c r="D79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>2609288MJX34JS</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>2609288NAJ9N5T</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr"/>
-      <c r="C81" s="5" t="inlineStr"/>
-      <c r="D81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>2609288Q7S46T0</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr"/>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>2609288UG1C8JW</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="5" t="inlineStr"/>
-      <c r="D83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>2609288VQGYXT9</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr"/>
-      <c r="C84" s="5" t="inlineStr"/>
-      <c r="D84" s="5" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>26092993CB5115</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="5" t="inlineStr"/>
-      <c r="D85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>260929950VHJAA</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="5" t="inlineStr"/>
-      <c r="D86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>260929957NWA1G</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="5" t="inlineStr"/>
-      <c r="D87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>2609299TC890MQ</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr"/>
-      <c r="C88" s="5" t="inlineStr"/>
-      <c r="D88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>260929A52TQ85P</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr"/>
-      <c r="C89" s="5" t="inlineStr"/>
-      <c r="D89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>260929A6D8RQWB</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr"/>
-      <c r="C90" s="5" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>260929A6YJ9GT0</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr"/>
-      <c r="C91" s="5" t="inlineStr"/>
-      <c r="D91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>260929A8WD5J4D</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr"/>
-      <c r="C92" s="5" t="inlineStr"/>
-      <c r="D92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>260929A9FF4P5G</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr"/>
-      <c r="C93" s="5" t="inlineStr"/>
-      <c r="D93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>260929A9MRW7MD</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr"/>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>260929AA0A02S8</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr"/>
-      <c r="C95" s="5" t="inlineStr"/>
-      <c r="D95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>260929ABEXF2A4</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr"/>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>260929ABKUSD4M</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr"/>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>260929ABYQBR26</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr"/>
-      <c r="C98" s="5" t="inlineStr"/>
-      <c r="D98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>260929AC46E1GX</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr"/>
-      <c r="C99" s="5" t="inlineStr"/>
-      <c r="D99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>260929AD47N1M5</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr"/>
-      <c r="C100" s="5" t="inlineStr"/>
-      <c r="D100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>260929AFRDRNNR</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr"/>
-      <c r="C101" s="5" t="inlineStr"/>
-      <c r="D101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>260929AGS030JM</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr"/>
-      <c r="C102" s="5" t="inlineStr"/>
-      <c r="D102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>260929AH6XDMBG</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr"/>
-      <c r="C103" s="5" t="inlineStr"/>
-      <c r="D103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>260929AKH7WXDK</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr"/>
-      <c r="C104" s="5" t="inlineStr"/>
-      <c r="D104" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D104"/>
+  <autoFilter ref="A1:D33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1330,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D729"/>
+  <dimension ref="A1:D734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -1340,22 +818,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>failed_category</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>failed_reason</t>
         </is>
@@ -19403,7 +18881,7 @@
     <row r="688">
       <c r="A688" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08:02</t>
+          <t>2026-09-29 16:08:52</t>
         </is>
       </c>
       <c r="B688" s="5" t="inlineStr">
@@ -19413,37 +18891,10 @@
       </c>
       <c r="C688" s="5" t="inlineStr">
         <is>
-          <t>2609262QDA21GD</t>
+          <t>2609262RUEB5XK</t>
         </is>
       </c>
       <c r="D688" s="5" t="inlineStr">
-        <is>
-          <t>Order skipped, CP/DC not set for SKU: SP1-001420+SP1-001421+SP1-001422+SP1-001423 (วันที่: 2026-09-26 10:51, ราคาที่ต้องออกบิล: 9673.0)
-SHOPEE เวลาสั่งซื้อ 2026-09-26 10:51
-SP1-001420+SP1-001421+SP1-001422+SP1-001423 BROTHER ตลับผงหมึก(โทนเนอร์) รุ่น TN-263 BK / C / M / Y และ PACK 4 สี
-ยิงขายขึ้น 11,500.00 บาท
-ลูกค้าซื้อราคา 9,673.00 บาท
-ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:08:52</t>
-        </is>
-      </c>
-      <c r="B689" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C689" s="5" t="inlineStr">
-        <is>
-          <t>2609262RUEB5XK</t>
-        </is>
-      </c>
-      <c r="D689" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 11:16, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 11:16
@@ -19454,23 +18905,23 @@
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" s="5" t="inlineStr">
+    <row r="689">
+      <c r="A689" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:09:52</t>
         </is>
       </c>
-      <c r="B690" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C690" s="5" t="inlineStr">
+      <c r="B689" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C689" s="5" t="inlineStr">
         <is>
           <t>2609262SDTRJKT</t>
         </is>
       </c>
-      <c r="D690" s="5" t="inlineStr">
+      <c r="D689" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 11:27, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 11:27
@@ -19481,23 +18932,23 @@
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" s="5" t="inlineStr">
+    <row r="690">
+      <c r="A690" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:11:08</t>
         </is>
       </c>
-      <c r="B691" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C691" s="5" t="inlineStr">
+      <c r="B690" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C690" s="5" t="inlineStr">
         <is>
           <t>2609262UF0E1VB</t>
         </is>
       </c>
-      <c r="D691" s="5" t="inlineStr">
+      <c r="D690" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-26 12:03, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 12:03
@@ -19508,23 +18959,23 @@
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" s="5" t="inlineStr">
+    <row r="691">
+      <c r="A691" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:11:50</t>
         </is>
       </c>
-      <c r="B692" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C692" s="5" t="inlineStr">
+      <c r="B691" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C691" s="5" t="inlineStr">
         <is>
           <t>26092631GEQ8KP</t>
         </is>
       </c>
-      <c r="D692" s="5" t="inlineStr">
+      <c r="D691" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001858+SP2-001859 (วันที่: 2026-09-26 13:51, ราคาที่ต้องออกบิล: 1820.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 13:51
@@ -19535,23 +18986,23 @@
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" s="5" t="inlineStr">
+    <row r="692">
+      <c r="A692" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:12:36</t>
         </is>
       </c>
-      <c r="B693" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C693" s="5" t="inlineStr">
+      <c r="B692" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C692" s="5" t="inlineStr">
         <is>
           <t>26092631WTVYJ3</t>
         </is>
       </c>
-      <c r="D693" s="5" t="inlineStr">
+      <c r="D692" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 13:59, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 13:59
@@ -19562,23 +19013,23 @@
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" s="5" t="inlineStr">
+    <row r="693">
+      <c r="A693" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:13:23</t>
         </is>
       </c>
-      <c r="B694" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C694" s="5" t="inlineStr">
+      <c r="B693" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C693" s="5" t="inlineStr">
         <is>
           <t>26092633MB47DQ</t>
         </is>
       </c>
-      <c r="D694" s="5" t="inlineStr">
+      <c r="D693" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 14:29, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 14:29
@@ -19589,23 +19040,23 @@
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" s="5" t="inlineStr">
+    <row r="694">
+      <c r="A694" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:14:18</t>
         </is>
       </c>
-      <c r="B695" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C695" s="5" t="inlineStr">
+      <c r="B694" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C694" s="5" t="inlineStr">
         <is>
           <t>260926347M7FKK</t>
         </is>
       </c>
-      <c r="D695" s="5" t="inlineStr">
+      <c r="D694" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-26 14:40, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 14:40
@@ -19616,23 +19067,23 @@
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" s="5" t="inlineStr">
+    <row r="695">
+      <c r="A695" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:15:06</t>
         </is>
       </c>
-      <c r="B696" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C696" s="5" t="inlineStr">
+      <c r="B695" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C695" s="5" t="inlineStr">
         <is>
           <t>26092635VWD1P9</t>
         </is>
       </c>
-      <c r="D696" s="5" t="inlineStr">
+      <c r="D695" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 15:10, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 15:10
@@ -19643,23 +19094,23 @@
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" s="5" t="inlineStr">
+    <row r="696">
+      <c r="A696" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:15:59</t>
         </is>
       </c>
-      <c r="B697" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C697" s="5" t="inlineStr">
+      <c r="B696" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C696" s="5" t="inlineStr">
         <is>
           <t>2609263QJF6YBP</t>
         </is>
       </c>
-      <c r="D697" s="5" t="inlineStr">
+      <c r="D696" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-26 20:26, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 20:26
@@ -19670,23 +19121,23 @@
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" s="5" t="inlineStr">
+    <row r="697">
+      <c r="A697" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:16:48</t>
         </is>
       </c>
-      <c r="B698" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C698" s="5" t="inlineStr">
+      <c r="B697" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C697" s="5" t="inlineStr">
         <is>
           <t>2609263TMY3K01</t>
         </is>
       </c>
-      <c r="D698" s="5" t="inlineStr">
+      <c r="D697" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001778+SP2-001779 (วันที่: 2026-09-26 21:21, ราคาที่ต้องออกบิล: 832.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-26 21:21
@@ -19701,23 +19152,23 @@
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" s="5" t="inlineStr">
+    <row r="698">
+      <c r="A698" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:17:42</t>
         </is>
       </c>
-      <c r="B699" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C699" s="5" t="inlineStr">
+      <c r="B698" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C698" s="5" t="inlineStr">
         <is>
           <t>260927445FQVAW</t>
         </is>
       </c>
-      <c r="D699" s="5" t="inlineStr">
+      <c r="D698" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-27 00:11, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 00:11
@@ -19728,23 +19179,23 @@
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" s="5" t="inlineStr">
+    <row r="699">
+      <c r="A699" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:18:28</t>
         </is>
       </c>
-      <c r="B700" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C700" s="5" t="inlineStr">
+      <c r="B699" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C699" s="5" t="inlineStr">
         <is>
           <t>26092744X1MGUB</t>
         </is>
       </c>
-      <c r="D700" s="5" t="inlineStr">
+      <c r="D699" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-27 00:25, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 00:25
@@ -19755,23 +19206,23 @@
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" s="5" t="inlineStr">
+    <row r="700">
+      <c r="A700" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:19:20</t>
         </is>
       </c>
-      <c r="B701" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C701" s="5" t="inlineStr">
+      <c r="B700" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C700" s="5" t="inlineStr">
         <is>
           <t>2609274FB4UJDG</t>
         </is>
       </c>
-      <c r="D701" s="5" t="inlineStr">
+      <c r="D700" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP1-001420+SP1-001421+SP1-001422+SP1-001423 (วันที่: 2026-09-27 03:32, ราคาที่ต้องออกบิล: 9673.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 03:32
@@ -19782,23 +19233,23 @@
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" s="5" t="inlineStr">
+    <row r="701">
+      <c r="A701" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:28:02</t>
         </is>
       </c>
-      <c r="B702" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C702" s="5" t="inlineStr">
+      <c r="B701" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C701" s="5" t="inlineStr">
         <is>
           <t>26092755XN57NG</t>
         </is>
       </c>
-      <c r="D702" s="5" t="inlineStr">
+      <c r="D701" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-27 10:16, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 10:16
@@ -19809,23 +19260,23 @@
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" s="5" t="inlineStr">
+    <row r="702">
+      <c r="A702" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:28:55</t>
         </is>
       </c>
-      <c r="B703" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C703" s="5" t="inlineStr">
+      <c r="B702" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C702" s="5" t="inlineStr">
         <is>
           <t>2609275HJYEURA</t>
         </is>
       </c>
-      <c r="D703" s="5" t="inlineStr">
+      <c r="D702" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-27 13:44, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 13:44
@@ -19836,23 +19287,23 @@
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" s="5" t="inlineStr">
+    <row r="703">
+      <c r="A703" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:29:36</t>
         </is>
       </c>
-      <c r="B704" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C704" s="5" t="inlineStr">
+      <c r="B703" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C703" s="5" t="inlineStr">
         <is>
           <t>2609275YYBRJHV</t>
         </is>
       </c>
-      <c r="D704" s="5" t="inlineStr">
+      <c r="D703" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-27 18:02, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 18:02
@@ -19863,23 +19314,23 @@
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" s="5" t="inlineStr">
+    <row r="704">
+      <c r="A704" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:30:27</t>
         </is>
       </c>
-      <c r="B705" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C705" s="5" t="inlineStr">
+      <c r="B704" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C704" s="5" t="inlineStr">
         <is>
           <t>260927648CQYQY</t>
         </is>
       </c>
-      <c r="D705" s="5" t="inlineStr">
+      <c r="D704" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP4-000302 (วันที่: 2026-09-27 19:18, ราคาที่ต้องออกบิล: 141.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 19:18
@@ -19894,23 +19345,23 @@
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" s="5" t="inlineStr">
+    <row r="705">
+      <c r="A705" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:31:12</t>
         </is>
       </c>
-      <c r="B706" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C706" s="5" t="inlineStr">
+      <c r="B705" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C705" s="5" t="inlineStr">
         <is>
           <t>26092766UT5CX6</t>
         </is>
       </c>
-      <c r="D706" s="5" t="inlineStr">
+      <c r="D705" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP1-001445+SP1-001446+SP1-001447+SP1-001448 (วันที่: 2026-09-27 20:05, ราคาที่ต้องออกบิล: 11997.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 20:05
@@ -19921,23 +19372,23 @@
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" s="5" t="inlineStr">
+    <row r="706">
+      <c r="A706" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:31:59</t>
         </is>
       </c>
-      <c r="B707" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C707" s="5" t="inlineStr">
+      <c r="B706" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C706" s="5" t="inlineStr">
         <is>
           <t>26092768VXTEBB</t>
         </is>
       </c>
-      <c r="D707" s="5" t="inlineStr">
+      <c r="D706" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-27 20:42, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-27 20:42
@@ -19948,50 +19399,23 @@
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:32:48</t>
-        </is>
-      </c>
-      <c r="B708" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C708" s="5" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="D708" s="5" t="inlineStr">
-        <is>
-          <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-28 08:48, ราคาที่ต้องออกบิล: 1449.0)
-SHOPEE เวลาสั่งซื้อ 2026-09-28 08:48
-SP2-001792+SP2-001793+SP2-001794+SP2-001795 Canon ตลับหมึกอิงค์เจ็ท รุ่น GI 71 BK / C / M / Y และ PACK 4 สี
-ยิงขายขึ้น 1,920.00 บาท
-ลูกค้าซื้อราคา 1,449.00 บาท
-ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" s="5" t="inlineStr">
+    <row r="707">
+      <c r="A707" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:33:32</t>
         </is>
       </c>
-      <c r="B709" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C709" s="5" t="inlineStr">
+      <c r="B707" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C707" s="5" t="inlineStr">
         <is>
           <t>2609287KHRAXC7</t>
         </is>
       </c>
-      <c r="D709" s="5" t="inlineStr">
+      <c r="D707" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 09:25, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 09:25
@@ -20002,23 +19426,23 @@
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" s="5" t="inlineStr">
+    <row r="708">
+      <c r="A708" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:34:08</t>
         </is>
       </c>
-      <c r="B710" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C710" s="5" t="inlineStr">
+      <c r="B708" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C708" s="5" t="inlineStr">
         <is>
           <t>2609287M80Q5UP</t>
         </is>
       </c>
-      <c r="D710" s="5" t="inlineStr">
+      <c r="D708" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001869+SP2-001870 (วันที่: 2026-09-28 09:37, ราคาที่ต้องออกบิล: 903.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 09:37
@@ -20029,23 +19453,23 @@
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" s="5" t="inlineStr">
+    <row r="709">
+      <c r="A709" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:38:59</t>
         </is>
       </c>
-      <c r="B711" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C711" s="5" t="inlineStr">
+      <c r="B709" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C709" s="5" t="inlineStr">
         <is>
           <t>2609287MW9NK93</t>
         </is>
       </c>
-      <c r="D711" s="5" t="inlineStr">
+      <c r="D709" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001799+SP2-001800+SP2-001801+SP2-001802 (วันที่: 2026-09-28 09:49, ราคาที่ต้องออกบิล: 1849.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 09:49
@@ -20056,23 +19480,23 @@
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" s="5" t="inlineStr">
+    <row r="710">
+      <c r="A710" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:39:45</t>
         </is>
       </c>
-      <c r="B712" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C712" s="5" t="inlineStr">
+      <c r="B710" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C710" s="5" t="inlineStr">
         <is>
           <t>2609287NJA0VU4</t>
         </is>
       </c>
-      <c r="D712" s="5" t="inlineStr">
+      <c r="D710" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001749+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-09-28 10:01, ราคาที่ต้องออกบิล: 1241.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 10:01
@@ -20083,23 +19507,23 @@
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" s="5" t="inlineStr">
+    <row r="711">
+      <c r="A711" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:40:47</t>
         </is>
       </c>
-      <c r="B713" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C713" s="5" t="inlineStr">
+      <c r="B711" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C711" s="5" t="inlineStr">
         <is>
           <t>2609287P01PS20</t>
         </is>
       </c>
-      <c r="D713" s="5" t="inlineStr">
+      <c r="D711" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 10:09, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 10:09
@@ -20110,23 +19534,23 @@
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" s="5" t="inlineStr">
+    <row r="712">
+      <c r="A712" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:41:38</t>
         </is>
       </c>
-      <c r="B714" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C714" s="5" t="inlineStr">
+      <c r="B712" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C712" s="5" t="inlineStr">
         <is>
           <t>2609287PH6YMU1</t>
         </is>
       </c>
-      <c r="D714" s="5" t="inlineStr">
+      <c r="D712" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 10:18, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 10:18
@@ -20137,23 +19561,23 @@
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" s="5" t="inlineStr">
+    <row r="713">
+      <c r="A713" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:42:38</t>
         </is>
       </c>
-      <c r="B715" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C715" s="5" t="inlineStr">
+      <c r="B713" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C713" s="5" t="inlineStr">
         <is>
           <t>2609287R198143</t>
         </is>
       </c>
-      <c r="D715" s="5" t="inlineStr">
+      <c r="D713" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-28 10:45, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 10:45
@@ -20164,23 +19588,23 @@
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" s="5" t="inlineStr">
+    <row r="714">
+      <c r="A714" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:43:36</t>
         </is>
       </c>
-      <c r="B716" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C716" s="5" t="inlineStr">
+      <c r="B714" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C714" s="5" t="inlineStr">
         <is>
           <t>2609287RT9BH89</t>
         </is>
       </c>
-      <c r="D716" s="5" t="inlineStr">
+      <c r="D714" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-28 10:59, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 10:59
@@ -20191,23 +19615,23 @@
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" s="5" t="inlineStr">
+    <row r="715">
+      <c r="A715" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:44:24</t>
         </is>
       </c>
-      <c r="B717" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C717" s="5" t="inlineStr">
+      <c r="B715" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C715" s="5" t="inlineStr">
         <is>
           <t>2609287SDKC5RV</t>
         </is>
       </c>
-      <c r="D717" s="5" t="inlineStr">
+      <c r="D715" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001858+SP2-001859 (วันที่: 2026-09-28 11:10, ราคาที่ต้องออกบิล: 1861.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 11:10
@@ -20222,23 +19646,23 @@
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" s="5" t="inlineStr">
+    <row r="716">
+      <c r="A716" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:45:09</t>
         </is>
       </c>
-      <c r="B718" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C718" s="5" t="inlineStr">
+      <c r="B716" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C716" s="5" t="inlineStr">
         <is>
           <t>2609287U5U0A9M</t>
         </is>
       </c>
-      <c r="D718" s="5" t="inlineStr">
+      <c r="D716" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-28 11:41, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 11:41
@@ -20249,23 +19673,23 @@
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" s="5" t="inlineStr">
+    <row r="717">
+      <c r="A717" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:45:56</t>
         </is>
       </c>
-      <c r="B719" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C719" s="5" t="inlineStr">
+      <c r="B717" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C717" s="5" t="inlineStr">
         <is>
           <t>2609287U7UTWXR</t>
         </is>
       </c>
-      <c r="D719" s="5" t="inlineStr">
+      <c r="D717" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-28 11:42, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 11:42
@@ -20276,23 +19700,23 @@
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" s="5" t="inlineStr">
+    <row r="718">
+      <c r="A718" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:46:47</t>
         </is>
       </c>
-      <c r="B720" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C720" s="5" t="inlineStr">
+      <c r="B718" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C718" s="5" t="inlineStr">
         <is>
           <t>2609287VFUP3AC</t>
         </is>
       </c>
-      <c r="D720" s="5" t="inlineStr">
+      <c r="D718" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 12:05, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:05
@@ -20303,23 +19727,23 @@
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" s="5" t="inlineStr">
+    <row r="719">
+      <c r="A719" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:47:28</t>
         </is>
       </c>
-      <c r="B721" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C721" s="5" t="inlineStr">
+      <c r="B719" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C719" s="5" t="inlineStr">
         <is>
           <t>2609287VPK6F3M</t>
         </is>
       </c>
-      <c r="D721" s="5" t="inlineStr">
+      <c r="D719" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-28 12:09, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:09
@@ -20330,23 +19754,23 @@
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" s="5" t="inlineStr">
+    <row r="720">
+      <c r="A720" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:48:28</t>
         </is>
       </c>
-      <c r="B722" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C722" s="5" t="inlineStr">
+      <c r="B720" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C720" s="5" t="inlineStr">
         <is>
           <t>2609287VXX5E41</t>
         </is>
       </c>
-      <c r="D722" s="5" t="inlineStr">
+      <c r="D720" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-28 12:13, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:13
@@ -20357,23 +19781,23 @@
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" s="5" t="inlineStr">
+    <row r="721">
+      <c r="A721" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:49:16</t>
         </is>
       </c>
-      <c r="B723" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C723" s="5" t="inlineStr">
+      <c r="B721" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C721" s="5" t="inlineStr">
         <is>
           <t>2609287W5Y7F6V</t>
         </is>
       </c>
-      <c r="D723" s="5" t="inlineStr">
+      <c r="D721" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-28 12:17, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:17
@@ -20384,23 +19808,23 @@
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" s="5" t="inlineStr">
+    <row r="722">
+      <c r="A722" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:50:03</t>
         </is>
       </c>
-      <c r="B724" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C724" s="5" t="inlineStr">
+      <c r="B722" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C722" s="5" t="inlineStr">
         <is>
           <t>2609287XBTEAVC</t>
         </is>
       </c>
-      <c r="D724" s="5" t="inlineStr">
+      <c r="D722" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 12:38, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:38
@@ -20411,23 +19835,23 @@
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" s="5" t="inlineStr">
+    <row r="723">
+      <c r="A723" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:50:53</t>
         </is>
       </c>
-      <c r="B725" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C725" s="5" t="inlineStr">
+      <c r="B723" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C723" s="5" t="inlineStr">
         <is>
           <t>2609287Y6Y7P0J</t>
         </is>
       </c>
-      <c r="D725" s="5" t="inlineStr">
+      <c r="D723" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 12:53, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 12:53
@@ -20438,23 +19862,23 @@
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" s="5" t="inlineStr">
+    <row r="724">
+      <c r="A724" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:51:50</t>
         </is>
       </c>
-      <c r="B726" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C726" s="5" t="inlineStr">
+      <c r="B724" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C724" s="5" t="inlineStr">
         <is>
           <t>26092882JSKG0Y</t>
         </is>
       </c>
-      <c r="D726" s="5" t="inlineStr">
+      <c r="D724" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 13:54, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 13:54
@@ -20465,23 +19889,23 @@
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" s="5" t="inlineStr">
+    <row r="725">
+      <c r="A725" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:52:33</t>
         </is>
       </c>
-      <c r="B727" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C727" s="5" t="inlineStr">
+      <c r="B725" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C725" s="5" t="inlineStr">
         <is>
           <t>2609288340UQ6V</t>
         </is>
       </c>
-      <c r="D727" s="5" t="inlineStr">
+      <c r="D725" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 14:03, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 14:03
@@ -20492,23 +19916,23 @@
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" s="5" t="inlineStr">
+    <row r="726">
+      <c r="A726" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:53:16</t>
         </is>
       </c>
-      <c r="B728" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C728" s="5" t="inlineStr">
+      <c r="B726" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C726" s="5" t="inlineStr">
         <is>
           <t>2609288357127B</t>
         </is>
       </c>
-      <c r="D728" s="5" t="inlineStr">
+      <c r="D726" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-28 14:04, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 14:04
@@ -20519,23 +19943,23 @@
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" s="5" t="inlineStr">
+    <row r="727">
+      <c r="A727" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:54:05</t>
         </is>
       </c>
-      <c r="B729" s="5" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C729" s="5" t="inlineStr">
+      <c r="B727" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C727" s="5" t="inlineStr">
         <is>
           <t>260928839XM3DT</t>
         </is>
       </c>
-      <c r="D729" s="5" t="inlineStr">
+      <c r="D727" s="5" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-28 14:07, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 14:07
@@ -20546,83 +19970,276 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:30:06</t>
+        </is>
+      </c>
+      <c r="B728" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C728" s="5" t="inlineStr">
+        <is>
+          <t>2609262QDA21GD</t>
+        </is>
+      </c>
+      <c r="D728" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP1-001420+SP1-001421+SP1-001422+SP1-001423 (วันที่: 2026-09-26 10:51, ราคาที่ต้องออกบิล: 9673.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-26 10:51
+SP1-001420+SP1-001421+SP1-001422+SP1-001423 BROTHER ตลับผงหมึก(โทนเนอร์) รุ่น TN-263 BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 11,500.00 บาท
+ลูกค้าซื้อราคา 9,673.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 9,673.00 บาท พอดีเป๊ะ:
+   • แนะนำ: 'CP2609090005' (ส่วนลด 321.00 บาท)
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:31:05</t>
+        </is>
+      </c>
+      <c r="B729" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C729" s="5" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="D729" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-28 08:48, ราคาที่ต้องออกบิล: 1449.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-28 08:48
+SP2-001792+SP2-001793+SP2-001794+SP2-001795 Canon ตลับหมึกอิงค์เจ็ท รุ่น GI 71 BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,920.00 บาท
+ลูกค้าซื้อราคา 1,449.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:32:09</t>
+        </is>
+      </c>
+      <c r="B730" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C730" s="5" t="inlineStr">
+        <is>
+          <t>2609288CCHXCUX</t>
+        </is>
+      </c>
+      <c r="D730" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP1-001445+SP1-001446+SP1-001447+SP1-001448 (วันที่: 2026-09-28 16:49, ราคาที่ต้องออกบิล: 11997.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-28 16:49
+SP1-001445+SP1-001446+SP1-001447+SP1-001448 CANON Toner รุ่น CRT-054 BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 15,500.00 บาท
+ลูกค้าซื้อราคา 11,997.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:33:15</t>
+        </is>
+      </c>
+      <c r="B731" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C731" s="5" t="inlineStr">
+        <is>
+          <t>26092993CB5115</t>
+        </is>
+      </c>
+      <c r="D731" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-28 23:41, ราคาที่ต้องออกบิล: 1017.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-28 23:41
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 1,017.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:34:15</t>
+        </is>
+      </c>
+      <c r="B732" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C732" s="5" t="inlineStr">
+        <is>
+          <t>260929A6D8RQWB</t>
+        </is>
+      </c>
+      <c r="D732" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-29 10:08, ราคาที่ต้องออกบิล: 1449.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-29 10:08
+SP2-001792+SP2-001793+SP2-001794+SP2-001795 Canon ตลับหมึกอิงค์เจ็ท รุ่น GI 71 BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,920.00 บาท
+ลูกค้าซื้อราคา 1,449.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:35:20</t>
+        </is>
+      </c>
+      <c r="B733" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C733" s="5" t="inlineStr">
+        <is>
+          <t>260929A6YJ9GT0</t>
+        </is>
+      </c>
+      <c r="D733" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-29 10:18, ราคาที่ต้องออกบิล: 1234.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-29 10:18
+SP2-001610+SP2-001611+SP2-001612+SP2-001613 Canon หมึกอิงค์เจ็ท รุ่น GI 790 BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,500.00 บาท
+ลูกค้าซื้อราคา 1,234.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:41:07</t>
+        </is>
+      </c>
+      <c r="B734" s="5" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C734" s="5" t="inlineStr">
+        <is>
+          <t>260929A8NDNF0R</t>
+        </is>
+      </c>
+      <c r="D734" s="5" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001713+SP2-001714+SP2-001715+SP2-001716 (วันที่: 2026-09-29 10:48, ราคาที่ต้องออกบิล: 1199.0)
+SHOPEE เวลาสั่งซื้อ 2026-09-29 10:48
+SP2-001713+SP2-001714+SP2-001715+SP2-001716 Epson หมึกแท้รุ่น T00V (003) Ink Bottle BK / C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,400.00 บาท
+ลูกค้าซื้อราคา 1,199.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D729"/>
+  <autoFilter ref="A1:D734"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H115"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" style="6" min="1" max="1"/>
-    <col width="24" customWidth="1" style="6" min="2" max="2"/>
-    <col width="23" customWidth="1" style="6" min="3" max="3"/>
-    <col width="12" customWidth="1" style="6" min="4" max="4"/>
-    <col width="50" customWidth="1" style="6" min="5" max="5"/>
-    <col width="22" customWidth="1" style="6" min="6" max="6"/>
-    <col width="50" customWidth="1" style="6" min="7" max="7"/>
-    <col width="49" customWidth="1" style="6" min="8" max="8"/>
+    <col width="22" customWidth="1" style="5" min="1" max="1"/>
+    <col width="24" customWidth="1" style="5" min="2" max="2"/>
+    <col width="23" customWidth="1" style="5" min="3" max="3"/>
+    <col width="12" customWidth="1" style="5" min="4" max="4"/>
+    <col width="50" customWidth="1" style="5" min="5" max="5"/>
+    <col width="22" customWidth="1" style="5" min="6" max="6"/>
+    <col width="50" customWidth="1" style="5" min="7" max="7"/>
+    <col width="49" customWidth="1" style="5" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>tracking</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>bill_no</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>pricing_detail</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>sn</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
+    <row r="2" ht="15" customHeight="1" s="6">
+      <c r="A2" s="5" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
           <t>260705U8AWD8X6</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:00:36</t>
@@ -20633,18 +20250,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="6">
+      <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
           <t>260705URX5JBBC</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:00:41</t>
@@ -20655,18 +20272,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>260705UUUR5B4H</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:00:46</t>
@@ -20677,18 +20294,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="6">
+      <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>260705UXGAN2T5</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:00:51</t>
@@ -20699,18 +20316,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="6">
+      <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>260705V1BGX4AY</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:00:56</t>
@@ -20721,18 +20338,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="6">
+      <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>260706V7WUY4PB</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:01:01</t>
@@ -20743,18 +20360,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="6">
+      <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>260706VAXHM05Q</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:01:07</t>
@@ -20765,18 +20382,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>260706VBGRBJ14</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:01:12</t>
@@ -20787,18 +20404,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="6">
+      <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>260706W1H3GHG6</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:01:18</t>
@@ -20809,18 +20426,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="6">
+      <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>26070601E4GX2U</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026-07-06 17:01:23</t>
@@ -20831,18 +20448,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="6">
+      <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>2607302CEDFJS4</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026-07-31 17:10:22</t>
@@ -20853,9 +20470,9 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="6">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TH2681732963608</t>
@@ -20871,8 +20488,8 @@
           <t>B0183-W06-2607310006</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026-07-31 18:02:11</t>
@@ -20883,18 +20500,18 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="6">
+      <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>260727R6XHKWWC</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:07:33</t>
@@ -20905,18 +20522,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="6">
+      <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>2607301DAN98V5</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:07:58</t>
@@ -20927,18 +20544,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="6">
+      <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>26073020Q0WR1A</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:08:18</t>
@@ -20949,18 +20566,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="6">
+      <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>2607302DX82ATG</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:08:39</t>
@@ -20971,18 +20588,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="6">
+      <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>2607302SYK25FA</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:09:00</t>
@@ -20993,18 +20610,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="6">
+      <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
           <t>2607302VBMUERS</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:09:21</t>
@@ -21015,18 +20632,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="6">
+      <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>2607303M006MK6</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:09:42</t>
@@ -21037,18 +20654,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="6">
+      <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t>2607313VD5S929</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 12:10:08</t>
@@ -21059,18 +20676,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="6">
+      <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t>260801816XR1SA</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 14:09:55</t>
@@ -21081,9 +20698,9 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="6">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TH260202761573W</t>
@@ -21099,8 +20716,8 @@
           <t>B0183-W10-2608030001</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:00:06</t>
@@ -21111,18 +20728,18 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="6">
+      <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>2608029YR7VD5K</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:01:28</t>
@@ -21133,18 +20750,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="6">
+      <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
           <t>260802A1R1R8VB</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:06:27</t>
@@ -21155,18 +20772,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="6">
+      <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>260802A3WMJUJQ</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:11:22</t>
@@ -21177,18 +20794,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="6">
+      <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
           <t>260802A43BPRBQ</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:11:26</t>
@@ -21199,18 +20816,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="6">
+      <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
           <t>260802A5KSDP8Y</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:12:41</t>
@@ -21221,18 +20838,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="6">
+      <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="inlineStr">
         <is>
           <t>260802A7PW1G4Q</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:16:10</t>
@@ -21243,18 +20860,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="6">
+      <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
           <t>260802A842J310</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:16:43</t>
@@ -21265,18 +20882,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="6">
+      <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
           <t>260802A9MQY35U</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:21:19</t>
@@ -21287,18 +20904,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="6">
+      <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>260802A9Q0DV7T</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:21:58</t>
@@ -21309,18 +20926,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="6">
+      <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>260802AC7WMJYB</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:23:52</t>
@@ -21331,18 +20948,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="6">
+      <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
           <t>260802ACJM16P1</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:23:57</t>
@@ -21353,18 +20970,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="6">
+      <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
           <t>260802ADP00HEK</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:25:50</t>
@@ -21375,18 +20992,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="6">
+      <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
           <t>260802ADQS8H60</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:25:55</t>
@@ -21397,18 +21014,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="6">
+      <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
           <t>260802ADY6Q60N</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:26:00</t>
@@ -21419,18 +21036,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="6">
+      <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>260802AE0BVAJW</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:26:05</t>
@@ -21441,18 +21058,18 @@
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="6">
+      <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
           <t>260802AE3PNQJH</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:26:21</t>
@@ -21463,18 +21080,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="6">
+      <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
           <t>260802AEF03XVG</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:26:48</t>
@@ -21485,18 +21102,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="6">
+      <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
           <t>260802AER9QJXJ</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:27:37</t>
@@ -21507,18 +21124,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="6">
+      <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>260802AFA6TRJ3</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:28:15</t>
@@ -21529,18 +21146,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="6">
+      <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
           <t>260802AFTVX8MH</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:30:09</t>
@@ -21551,18 +21168,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="6">
+      <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
           <t>260802AG0YE9X0</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:30:14</t>
@@ -21573,18 +21190,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="6">
+      <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="inlineStr">
         <is>
           <t>260802AGE6W5NH</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:30:52</t>
@@ -21595,18 +21212,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="6">
+      <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="inlineStr">
         <is>
           <t>260802AH1KQNDA</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:31:24</t>
@@ -21617,18 +21234,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="6">
+      <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="inlineStr">
         <is>
           <t>260802AK1UT6UE</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:33:25</t>
@@ -21639,18 +21256,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="6">
+      <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="inlineStr">
         <is>
           <t>260802AK2B38BX</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:33:30</t>
@@ -21661,18 +21278,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="6">
+      <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="inlineStr">
         <is>
           <t>260802AKBKNJ35</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:33:35</t>
@@ -21683,18 +21300,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="6">
+      <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="inlineStr">
         <is>
           <t>260802AMFFXC5T</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:34:11</t>
@@ -21705,18 +21322,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="6">
+      <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="inlineStr">
         <is>
           <t>260802ANJ273J7</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:35:29</t>
@@ -21727,18 +21344,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="6">
+      <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="inlineStr">
         <is>
           <t>260802APD376V4</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:36:33</t>
@@ -21749,18 +21366,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="6">
+      <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="inlineStr">
         <is>
           <t>260802APSQGM14</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
       <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:37:42</t>
@@ -21771,18 +21388,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="6">
+      <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="inlineStr">
         <is>
           <t>260802AQHYT398</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:38:46</t>
@@ -21793,18 +21410,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="6">
+      <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="inlineStr">
         <is>
           <t>260802AR4G2WC0</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:39:59</t>
@@ -21815,18 +21432,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="6">
+      <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="inlineStr">
         <is>
           <t>260802ASEQDMP9</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:40:31</t>
@@ -21837,18 +21454,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="6">
+      <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="inlineStr">
         <is>
           <t>260802ASYP2F23</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:43:18</t>
@@ -21859,18 +21476,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="6">
+      <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="inlineStr">
         <is>
           <t>260802AT5Y80SH</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:43:23</t>
@@ -21881,18 +21498,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="6">
+      <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="inlineStr">
         <is>
           <t>260802AU8XW57M</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
       <c r="F59" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:45:08</t>
@@ -21903,18 +21520,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="6">
+      <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="inlineStr">
         <is>
           <t>260802AUAJE32U</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:45:13</t>
@@ -21925,18 +21542,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="6">
+      <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="inlineStr">
         <is>
           <t>260802AUKYS0M8</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
       <c r="F61" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:45:17</t>
@@ -21947,18 +21564,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="6">
+      <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="inlineStr">
         <is>
           <t>260802AUXTUXWT</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:45:22</t>
@@ -21969,18 +21586,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="6">
+      <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="inlineStr">
         <is>
           <t>260802AVW4SYRY</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:46:09</t>
@@ -21991,18 +21608,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="6">
+      <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="inlineStr">
         <is>
           <t>260802AVXNEK7R</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:46:14</t>
@@ -22013,18 +21630,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="6">
+      <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="inlineStr">
         <is>
           <t>260802AWUNAD3Q</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
       <c r="F65" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:46:47</t>
@@ -22035,18 +21652,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="6">
+      <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="inlineStr">
         <is>
           <t>260802AWVWDKG5</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:47:15</t>
@@ -22057,18 +21674,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="6">
+      <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="inlineStr">
         <is>
           <t>260802AXWT75VY</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:49:13</t>
@@ -22079,18 +21696,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="6">
+      <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="inlineStr">
         <is>
           <t>260802AY92PDCY</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
       <c r="F68" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:49:57</t>
@@ -22101,18 +21718,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="6">
+      <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="inlineStr">
         <is>
           <t>260802AYH72PNX</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:50:04</t>
@@ -22123,18 +21740,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="6">
+      <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="inlineStr">
         <is>
           <t>260802B0DSP265</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:51:25</t>
@@ -22145,18 +21762,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="6">
+      <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="inlineStr">
         <is>
           <t>260802B0RHWTA5</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
       <c r="F71" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:51:30</t>
@@ -22167,18 +21784,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="6">
+      <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="inlineStr">
         <is>
           <t>260802B1CUD6KB</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
       <c r="F72" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:52:22</t>
@@ -22189,18 +21806,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="6">
+      <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="inlineStr">
         <is>
           <t>260802B1FCF44E</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
       <c r="F73" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:52:56</t>
@@ -22211,18 +21828,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="6">
+      <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="inlineStr">
         <is>
           <t>260802B1H8JUN3</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:53:03</t>
@@ -22233,18 +21850,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="6">
+      <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="inlineStr">
         <is>
           <t>260802B286VHRP</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr"/>
-      <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="5" t="inlineStr"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
       <c r="F75" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:54:13</t>
@@ -22255,18 +21872,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="6">
+      <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="inlineStr">
         <is>
           <t>260802B3S01HQ5</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="inlineStr">
         <is>
           <t>2026-08-03 17:56:14</t>
@@ -22277,18 +21894,18 @@
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="6">
+      <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="inlineStr">
         <is>
           <t>260804EUH578AA</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
       <c r="F77" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 10:19:42</t>
@@ -22299,18 +21916,18 @@
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="6">
+      <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="inlineStr">
         <is>
           <t>260804ET95AQ30</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
       <c r="F78" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 10:22:55</t>
@@ -22321,18 +21938,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="6">
+      <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="inlineStr">
         <is>
           <t>260804EJ0NHM2E</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr"/>
-      <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="5" t="inlineStr"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 10:43:17</t>
@@ -22343,18 +21960,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="6">
+      <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="inlineStr">
         <is>
           <t>260804DUUQFTJG</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 11:00:57</t>
@@ -22365,18 +21982,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="6">
+      <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="inlineStr">
         <is>
           <t>260803DPXGUSUV</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr"/>
-      <c r="D81" s="5" t="inlineStr"/>
-      <c r="E81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 11:09:31</t>
@@ -22387,18 +22004,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="6">
+      <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="inlineStr">
         <is>
           <t>260803DP8F3NS6</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
       <c r="F82" s="5" t="inlineStr">
         <is>
           <t>2026-08-04 11:13:04</t>
@@ -22409,18 +22026,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="6">
+      <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="inlineStr">
         <is>
           <t>260805HDG148NB</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr"/>
-      <c r="D83" s="5" t="inlineStr"/>
-      <c r="E83" s="5" t="inlineStr"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 10:53:50</t>
@@ -22431,18 +22048,18 @@
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="6">
+      <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="inlineStr">
         <is>
           <t>260805HD7VR77Q</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr"/>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:07:59</t>
@@ -22453,18 +22070,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="6">
+      <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="inlineStr">
         <is>
           <t>260805HDQMBFQR</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr"/>
-      <c r="D85" s="5" t="inlineStr"/>
-      <c r="E85" s="5" t="inlineStr"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
       <c r="F85" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:11:08</t>
@@ -22475,18 +22092,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="6">
+      <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="inlineStr">
         <is>
           <t>260805HDCNAG7A</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr"/>
-      <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:11:57</t>
@@ -22497,18 +22114,18 @@
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr"/>
+      <c r="H86" s="5" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="6">
+      <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="inlineStr">
         <is>
           <t>260805HCA5Y6XM</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr"/>
-      <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
       <c r="F87" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:13:29</t>
@@ -22519,18 +22136,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
+      <c r="H87" s="5" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="6">
+      <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="inlineStr">
         <is>
           <t>260805H97WNP8E</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr"/>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:18:50</t>
@@ -22541,18 +22158,18 @@
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
+      <c r="H88" s="5" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="6">
+      <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="inlineStr">
         <is>
           <t>260805HA9UW4U4</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr"/>
-      <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="5" t="inlineStr"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
       <c r="F89" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:20:55</t>
@@ -22563,18 +22180,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="6">
+      <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="inlineStr">
         <is>
           <t>260805H9EYP2T3</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
       <c r="F90" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:21:20</t>
@@ -22585,18 +22202,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="6">
+      <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="inlineStr">
         <is>
           <t>260805H9GAN62D</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr"/>
-      <c r="D91" s="5" t="inlineStr"/>
-      <c r="E91" s="5" t="inlineStr"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
       <c r="F91" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:21:27</t>
@@ -22607,18 +22224,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="6">
+      <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="inlineStr">
         <is>
           <t>260805H7NMUJJU</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr"/>
-      <c r="D92" s="5" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:21:32</t>
@@ -22629,18 +22246,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="6">
+      <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="inlineStr">
         <is>
           <t>260805H98W4V8D</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr"/>
-      <c r="D93" s="5" t="inlineStr"/>
-      <c r="E93" s="5" t="inlineStr"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:21:38</t>
@@ -22651,18 +22268,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="6">
+      <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="inlineStr">
         <is>
           <t>260805H6DEAUGS</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
       <c r="F94" s="5" t="inlineStr">
         <is>
           <t>2026-08-05 17:22:17</t>
@@ -22673,18 +22290,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="6">
+      <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="inlineStr">
         <is>
           <t>260804ESV4MF8N</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr"/>
-      <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="5" t="inlineStr"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
       <c r="F95" s="5" t="inlineStr">
         <is>
           <t>2026-08-07 13:37:04</t>
@@ -22695,18 +22312,18 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="6">
+      <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="inlineStr">
         <is>
           <t>260807P7KTYK4X</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
       <c r="F96" s="5" t="inlineStr">
         <is>
           <t>2026-08-07 13:42:42</t>
@@ -22717,9 +22334,9 @@
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97">
+      <c r="H96" s="5" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="6">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>TH0116914HG21A</t>
@@ -22740,7 +22357,7 @@
           <t>18348</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="n"/>
       <c r="F97" s="5" t="inlineStr">
         <is>
           <t>2026-08-07 17:12:31</t>
@@ -22751,18 +22368,18 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="6">
+      <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="inlineStr">
         <is>
           <t>260807PW0ND922</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr"/>
-      <c r="D98" s="5" t="inlineStr"/>
-      <c r="E98" s="5" t="inlineStr"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
       <c r="F98" s="5" t="inlineStr">
         <is>
           <t>2026-08-07 17:19:05</t>
@@ -22773,18 +22390,18 @@
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
+      <c r="H98" s="5" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="6">
+      <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="inlineStr">
         <is>
           <t>260805JAVUPVE6</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr"/>
-      <c r="D99" s="5" t="inlineStr"/>
-      <c r="E99" s="5" t="inlineStr"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
       <c r="F99" s="5" t="inlineStr">
         <is>
           <t>2026-08-07 17:42:48</t>
@@ -22795,18 +22412,18 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="n"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="6">
+      <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="inlineStr">
         <is>
           <t>260819QP4Y7RAT</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr"/>
-      <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
       <c r="F100" s="5" t="inlineStr">
         <is>
           <t>2026-08-19 17:24:07</t>
@@ -22817,9 +22434,9 @@
           <t>ข้าม (สถานะ: จัดส่งสำเร็จแล้ว)</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101">
+      <c r="H100" s="5" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="6">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>TH261038221083X</t>
@@ -22840,7 +22457,7 @@
           <t>1200</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="n"/>
       <c r="F101" s="5" t="inlineStr">
         <is>
           <t>2026-08-19 17:28:00</t>
@@ -22851,18 +22468,18 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="6">
+      <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="inlineStr">
         <is>
           <t>260819QHMRC5EV</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr"/>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
       <c r="F102" s="5" t="inlineStr">
         <is>
           <t>2026-08-19 17:39:15</t>
@@ -22873,9 +22490,9 @@
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103">
+      <c r="H102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="6">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>TH040193X37H9N</t>
@@ -22886,9 +22503,9 @@
           <t>260901T0RGWX5K</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr"/>
-      <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
       <c r="F103" s="5" t="inlineStr">
         <is>
           <t>2026-09-01 16:28:51</t>
@@ -22899,9 +22516,9 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104">
+      <c r="H103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="6">
       <c r="A104" s="5" t="inlineStr">
         <is>
           <t>TH020493X3DW8C</t>
@@ -22912,9 +22529,9 @@
           <t>260901T4BAE22J</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr"/>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
       <c r="F104" s="5" t="inlineStr">
         <is>
           <t>2026-09-01 16:29:45</t>
@@ -22925,10 +22542,10 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="6">
+      <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="inlineStr">
         <is>
           <t>260901UNRKERUU</t>
@@ -22959,10 +22576,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="6">
+      <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="inlineStr">
         <is>
           <t>260901UNP2E131</t>
@@ -22993,10 +22610,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="6">
+      <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="inlineStr">
         <is>
           <t>260901UKYPXECQ</t>
@@ -23027,10 +22644,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="6">
+      <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="inlineStr">
         <is>
           <t>260901UK9402X5</t>
@@ -23061,10 +22678,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="6">
+      <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="inlineStr">
         <is>
           <t>260901UHVGCU1M</t>
@@ -23095,10 +22712,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="6">
+      <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="inlineStr">
         <is>
           <t>260901UNM86STV</t>
@@ -23129,10 +22746,10 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="6">
+      <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="inlineStr">
         <is>
           <t>260901UH2C0ECM</t>
@@ -23163,9 +22780,9 @@
           <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr"/>
-    </row>
-    <row r="112">
+      <c r="H111" s="5" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="6">
       <c r="A112" s="5" t="inlineStr">
         <is>
           <t>3242182671565824785</t>
@@ -23176,9 +22793,9 @@
           <t>260901UGKSNWX3</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr"/>
-      <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
       <c r="F112" s="5" t="inlineStr">
         <is>
           <t>2026-09-01 17:00:28</t>
@@ -23189,10 +22806,10 @@
           <t>ข้าม (สถานะ: จัดส่งสำเร็จแล้ว)</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="6">
+      <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="inlineStr">
         <is>
           <t>260901UF022TRC</t>
@@ -23223,9 +22840,9 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr"/>
-    </row>
-    <row r="114">
+      <c r="H113" s="5" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="6">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>TH2699150345208</t>
@@ -23267,7 +22884,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15" customHeight="1" s="6">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>TH269548592779K</t>
@@ -23278,9 +22895,9 @@
           <t>26092881JY2FWK</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr"/>
-      <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
       <c r="F115" s="5" t="inlineStr">
         <is>
           <t>2026-09-29 16:51:05</t>
@@ -23291,11 +22908,13 @@
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H115"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -23318,7 +22937,7 @@
     <row r="3" ht="13.5" customHeight="1" s="6"/>
     <row r="4" ht="13.5" customHeight="1" s="6"/>
     <row r="5" ht="12.75" customHeight="1" s="6">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>6K1CH8CL401874</t>
         </is>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Failed_Orders" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Completed_Orders" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Processed_Logs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +455,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>2609251AWCE1CK</t>
@@ -472,7 +472,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>MNL-002435</t>
@@ -490,7 +489,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>MMTDNST00B548025FC4288</t>
@@ -508,13 +506,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>MMTDNST00B55101D294288</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>MMV98ST001621011B63S00</t>
@@ -522,13 +518,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>MMV98ST00162100F463S00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>MMV98ST001611000C73S00</t>
@@ -536,24 +530,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>MMV98ST001621011B63S00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>MMV98ST001611000C73S00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11997,7 +11985,6 @@
           <t>ORDER_NOT_FOUND</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260805HF3RNVSQ ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
@@ -12015,7 +12002,6 @@
           <t>ORDER_NOT_FOUND</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260804G3B3XCSB ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
@@ -21589,21 +21575,16 @@
           <t>2026-07-06 17:00:36</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>260705U8AWD8X6</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21611,21 +21592,16 @@
           <t>2026-07-06 17:00:41</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>260705URX5JBBC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21633,21 +21609,16 @@
           <t>2026-07-06 17:00:46</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>260705UUUR5B4H</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21655,21 +21626,16 @@
           <t>2026-07-06 17:00:51</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>260705UXGAN2T5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21677,21 +21643,16 @@
           <t>2026-07-06 17:00:56</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>260705V1BGX4AY</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21699,21 +21660,16 @@
           <t>2026-07-06 17:01:01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>260706V7WUY4PB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21721,21 +21677,16 @@
           <t>2026-07-06 17:01:07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>260706VAXHM05Q</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21743,21 +21694,16 @@
           <t>2026-07-06 17:01:12</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>260706VBGRBJ14</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21765,21 +21711,16 @@
           <t>2026-07-06 17:01:18</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>260706W1H3GHG6</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21787,21 +21728,16 @@
           <t>2026-07-06 17:01:23</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>26070601E4GX2U</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21809,21 +21745,16 @@
           <t>2026-07-31 17:10:22</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>2607302CEDFJS4</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21846,14 +21777,11 @@
           <t>B0183-W06-2607310006</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21861,21 +21789,16 @@
           <t>2026-08-03 12:07:33</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>260727R6XHKWWC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21883,21 +21806,16 @@
           <t>2026-08-03 12:07:58</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>2607301DAN98V5</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21905,21 +21823,16 @@
           <t>2026-08-03 12:08:18</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>26073020Q0WR1A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21927,21 +21840,16 @@
           <t>2026-08-03 12:08:39</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>2607302DX82ATG</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21949,21 +21857,16 @@
           <t>2026-08-03 12:09:00</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>2607302SYK25FA</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21971,21 +21874,16 @@
           <t>2026-08-03 12:09:21</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>2607302VBMUERS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21993,21 +21891,16 @@
           <t>2026-08-03 12:09:42</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>2607303M006MK6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -22015,21 +21908,16 @@
           <t>2026-08-03 12:10:08</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>2607313VD5S929</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22037,21 +21925,16 @@
           <t>2026-08-03 14:09:55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>260801816XR1SA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22074,14 +21957,11 @@
           <t>B0183-W10-2608030001</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22089,21 +21969,16 @@
           <t>2026-08-03 17:01:28</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>2608029YR7VD5K</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22111,21 +21986,16 @@
           <t>2026-08-03 17:06:27</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>260802A1R1R8VB</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22133,21 +22003,16 @@
           <t>2026-08-03 17:11:22</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>260802A3WMJUJQ</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22155,21 +22020,16 @@
           <t>2026-08-03 17:11:26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>260802A43BPRBQ</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22177,21 +22037,16 @@
           <t>2026-08-03 17:12:41</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>260802A5KSDP8Y</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22199,21 +22054,16 @@
           <t>2026-08-03 17:16:10</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>260802A7PW1G4Q</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -22221,21 +22071,16 @@
           <t>2026-08-03 17:16:43</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>260802A842J310</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -22243,21 +22088,16 @@
           <t>2026-08-03 17:21:19</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>260802A9MQY35U</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -22265,21 +22105,16 @@
           <t>2026-08-03 17:21:58</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>260802A9Q0DV7T</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -22287,21 +22122,16 @@
           <t>2026-08-03 17:23:52</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>260802AC7WMJYB</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -22309,21 +22139,16 @@
           <t>2026-08-03 17:23:57</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>260802ACJM16P1</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -22331,21 +22156,16 @@
           <t>2026-08-03 17:25:50</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>260802ADP00HEK</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22353,21 +22173,16 @@
           <t>2026-08-03 17:25:55</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>260802ADQS8H60</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -22375,21 +22190,16 @@
           <t>2026-08-03 17:26:00</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>260802ADY6Q60N</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -22397,21 +22207,16 @@
           <t>2026-08-03 17:26:05</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>260802AE0BVAJW</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -22419,21 +22224,16 @@
           <t>2026-08-03 17:26:21</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>260802AE3PNQJH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22441,21 +22241,16 @@
           <t>2026-08-03 17:26:48</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>260802AEF03XVG</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22463,21 +22258,16 @@
           <t>2026-08-03 17:27:37</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>260802AER9QJXJ</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22485,21 +22275,16 @@
           <t>2026-08-03 17:28:15</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>260802AFA6TRJ3</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22507,21 +22292,16 @@
           <t>2026-08-03 17:30:09</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>260802AFTVX8MH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22529,21 +22309,16 @@
           <t>2026-08-03 17:30:14</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>260802AG0YE9X0</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22551,21 +22326,16 @@
           <t>2026-08-03 17:30:52</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>260802AGE6W5NH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -22573,21 +22343,16 @@
           <t>2026-08-03 17:31:24</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>260802AH1KQNDA</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22595,21 +22360,16 @@
           <t>2026-08-03 17:33:25</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>260802AK1UT6UE</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22617,21 +22377,16 @@
           <t>2026-08-03 17:33:30</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>260802AK2B38BX</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22639,21 +22394,16 @@
           <t>2026-08-03 17:33:35</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>260802AKBKNJ35</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22661,21 +22411,16 @@
           <t>2026-08-03 17:34:11</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>260802AMFFXC5T</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -22683,21 +22428,16 @@
           <t>2026-08-03 17:35:29</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>260802ANJ273J7</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -22705,21 +22445,16 @@
           <t>2026-08-03 17:36:33</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>260802APD376V4</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -22727,21 +22462,16 @@
           <t>2026-08-03 17:37:42</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>260802APSQGM14</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -22749,21 +22479,16 @@
           <t>2026-08-03 17:38:46</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>260802AQHYT398</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -22771,21 +22496,16 @@
           <t>2026-08-03 17:39:59</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>260802AR4G2WC0</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -22793,21 +22513,16 @@
           <t>2026-08-03 17:40:31</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>260802ASEQDMP9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22815,21 +22530,16 @@
           <t>2026-08-03 17:43:18</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>260802ASYP2F23</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22837,21 +22547,16 @@
           <t>2026-08-03 17:43:23</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>260802AT5Y80SH</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22859,21 +22564,16 @@
           <t>2026-08-03 17:45:08</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>260802AU8XW57M</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -22881,21 +22581,16 @@
           <t>2026-08-03 17:45:13</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>260802AUAJE32U</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -22903,21 +22598,16 @@
           <t>2026-08-03 17:45:17</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>260802AUKYS0M8</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22925,21 +22615,16 @@
           <t>2026-08-03 17:45:22</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>260802AUXTUXWT</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22947,21 +22632,16 @@
           <t>2026-08-03 17:46:09</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>260802AVW4SYRY</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22969,21 +22649,16 @@
           <t>2026-08-03 17:46:14</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>260802AVXNEK7R</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22991,21 +22666,16 @@
           <t>2026-08-03 17:46:47</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>260802AWUNAD3Q</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23013,21 +22683,16 @@
           <t>2026-08-03 17:47:15</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>260802AWVWDKG5</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -23035,21 +22700,16 @@
           <t>2026-08-03 17:49:13</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>260802AXWT75VY</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -23057,21 +22717,16 @@
           <t>2026-08-03 17:49:57</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>260802AY92PDCY</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23079,21 +22734,16 @@
           <t>2026-08-03 17:50:04</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>260802AYH72PNX</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23101,21 +22751,16 @@
           <t>2026-08-03 17:51:25</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>260802B0DSP265</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23123,21 +22768,16 @@
           <t>2026-08-03 17:51:30</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>260802B0RHWTA5</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -23145,21 +22785,16 @@
           <t>2026-08-03 17:52:22</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>260802B1CUD6KB</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23167,21 +22802,16 @@
           <t>2026-08-03 17:52:56</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>260802B1FCF44E</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23189,21 +22819,16 @@
           <t>2026-08-03 17:53:03</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>260802B1H8JUN3</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23211,21 +22836,16 @@
           <t>2026-08-03 17:54:13</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>260802B286VHRP</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23233,21 +22853,16 @@
           <t>2026-08-03 17:56:14</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>260802B3S01HQ5</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23255,21 +22870,16 @@
           <t>2026-08-04 10:19:42</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>260804EUH578AA</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23277,21 +22887,16 @@
           <t>2026-08-04 10:22:55</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>260804ET95AQ30</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23299,21 +22904,16 @@
           <t>2026-08-04 10:43:17</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>260804EJ0NHM2E</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -23321,21 +22921,16 @@
           <t>2026-08-04 11:00:57</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>260804DUUQFTJG</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -23343,21 +22938,16 @@
           <t>2026-08-04 11:09:31</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>260803DPXGUSUV</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23365,21 +22955,16 @@
           <t>2026-08-04 11:13:04</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>260803DP8F3NS6</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23387,21 +22972,16 @@
           <t>2026-08-05 10:53:50</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>260805HDG148NB</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23409,21 +22989,16 @@
           <t>2026-08-05 17:07:59</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>260805HD7VR77Q</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23431,21 +23006,16 @@
           <t>2026-08-05 17:11:08</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>260805HDQMBFQR</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23453,21 +23023,16 @@
           <t>2026-08-05 17:11:57</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>260805HDCNAG7A</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23475,21 +23040,16 @@
           <t>2026-08-05 17:13:29</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>260805HCA5Y6XM</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23497,21 +23057,16 @@
           <t>2026-08-05 17:18:50</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>260805H97WNP8E</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23519,21 +23074,16 @@
           <t>2026-08-05 17:20:55</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>260805HA9UW4U4</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23541,21 +23091,16 @@
           <t>2026-08-05 17:21:20</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>260805H9EYP2T3</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23563,21 +23108,16 @@
           <t>2026-08-05 17:21:27</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>260805H9GAN62D</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -23585,21 +23125,16 @@
           <t>2026-08-05 17:21:32</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>260805H7NMUJJU</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -23607,21 +23142,16 @@
           <t>2026-08-05 17:21:38</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>260805H98W4V8D</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -23629,21 +23159,16 @@
           <t>2026-08-05 17:22:17</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>260805H6DEAUGS</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -23651,21 +23176,16 @@
           <t>2026-08-07 13:37:04</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>260804ESV4MF8N</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -23673,21 +23193,16 @@
           <t>2026-08-07 13:42:42</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>260807P7KTYK4X</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (จบ process ปรับราคา)</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23713,13 +23228,11 @@
       <c r="E97" t="n">
         <v>18348</v>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23727,21 +23240,16 @@
           <t>2026-08-07 17:19:05</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>260807PW0ND922</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: รอการดำเนินการ)</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23749,21 +23257,16 @@
           <t>2026-08-07 17:42:48</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>260805JAVUPVE6</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23771,21 +23274,16 @@
           <t>2026-08-19 17:24:07</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>260819QP4Y7RAT</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: จัดส่งสำเร็จแล้ว)</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -23811,13 +23309,11 @@
       <c r="E101" t="n">
         <v>1200</v>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23825,21 +23321,16 @@
           <t>2026-08-19 17:39:15</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>260819QHMRC5EV</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -23857,15 +23348,11 @@
           <t>260901T0RGWX5K</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -23883,15 +23370,11 @@
           <t>260901T4BAE22J</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -23899,7 +23382,6 @@
           <t>2026-09-01 16:48:53</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>260901UNRKERUU</t>
@@ -23923,7 +23405,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -23931,7 +23412,6 @@
           <t>2026-09-01 16:49:30</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>260901UNP2E131</t>
@@ -23955,7 +23435,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -23963,7 +23442,6 @@
           <t>2026-09-01 16:51:14</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>260901UKYPXECQ</t>
@@ -23987,7 +23465,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -23995,7 +23472,6 @@
           <t>2026-09-01 16:52:05</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>260901UK9402X5</t>
@@ -24019,7 +23495,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -24027,7 +23502,6 @@
           <t>2026-09-01 16:53:32</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>260901UHVGCU1M</t>
@@ -24051,7 +23525,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -24059,7 +23532,6 @@
           <t>2026-09-01 16:56:46</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>260901UNM86STV</t>
@@ -24083,7 +23555,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -24091,7 +23562,6 @@
           <t>2026-09-01 16:59:46</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>260901UH2C0ECM</t>
@@ -24115,7 +23585,6 @@
           <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -24133,15 +23602,11 @@
           <t>260901UGKSNWX3</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: จัดส่งสำเร็จแล้ว)</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -24149,7 +23614,6 @@
           <t>2026-09-01 17:01:05</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>260901UF022TRC</t>
@@ -24173,7 +23637,6 @@
           <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -24231,15 +23694,11 @@
           <t>26092881JY2FWK</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -24265,13 +23724,11 @@
       <c r="E116" t="n">
         <v>9673</v>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (ปรับราคาผ่าน/All OK)</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -24297,13 +23754,11 @@
       <c r="E117" t="n">
         <v>1449</v>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (ปรับราคาผ่าน/All OK)</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -24311,7 +23766,6 @@
           <t>2026-10-01 11:10:49</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>26092993CB5115</t>
@@ -24325,13 +23779,11 @@
       <c r="E118" t="n">
         <v>1017</v>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (ปรับราคาผ่าน/All OK)</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24339,7 +23791,6 @@
           <t>2026-10-01 11:11:04</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>260929A9FF4P5G</t>
@@ -24353,13 +23804,11 @@
       <c r="E119" t="n">
         <v>959</v>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>TEST_SUCCESS (ปรับราคาผ่าน/All OK)</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24382,19 +23831,74 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>6K1CH8CL401874</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tracking</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>bill_no</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sn</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>remark</t>
         </is>
       </c>
     </row>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
@@ -13,7 +13,13 @@
     <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Processed_Logs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$785</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$H$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet4'!$A$1:$A$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Processed_Logs'!$A$1:$I$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -431,6 +437,12 @@
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -544,6 +556,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -554,8 +567,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -19742,7 +19761,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-09-30 16:31:05</t>
+          <t>2026-09-30 16:32:09</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -19752,37 +19771,10 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>2609287HFYKV3U</t>
+          <t>2609288CCHXCUX</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
-        <is>
-          <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-28 08:48, ราคาที่ต้องออกบิล: 1449.0)
-SHOPEE เวลาสั่งซื้อ 2026-09-28 08:48
-SP2-001792+SP2-001793+SP2-001794+SP2-001795 Canon ตลับหมึกอิงค์เจ็ท รุ่น GI 71 BK / C / M / Y และ PACK 4 สี
-ยิงขายขึ้น 1,920.00 บาท
-ลูกค้าซื้อราคา 1,449.00 บาท
-ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:32:09</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t>2609288CCHXCUX</t>
-        </is>
-      </c>
-      <c r="D730" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP1-001445+SP1-001446+SP1-001447+SP1-001448 (วันที่: 2026-09-28 16:49, ราคาที่ต้องออกบิล: 11997.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 16:49
@@ -19793,23 +19785,23 @@
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t>2026-09-30 16:33:15</t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
         <is>
           <t>26092993CB5115</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr">
+      <c r="D730" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-28 23:41, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-28 23:41
@@ -19820,23 +19812,23 @@
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t>2026-09-30 16:34:15</t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
         <is>
           <t>260929A6D8RQWB</t>
         </is>
       </c>
-      <c r="D732" t="inlineStr">
+      <c r="D731" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-29 10:08, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-29 10:08
@@ -19847,23 +19839,23 @@
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t>2026-09-30 16:35:20</t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C733" t="inlineStr">
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
         <is>
           <t>260929A6YJ9GT0</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr">
+      <c r="D732" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-29 10:18, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-29 10:18
@@ -19874,23 +19866,23 @@
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t>2026-09-30 16:41:07</t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
         <is>
           <t>260929A8NDNF0R</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr">
+      <c r="D733" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001713+SP2-001714+SP2-001715+SP2-001716 (วันที่: 2026-09-29 10:48, ราคาที่ต้องออกบิล: 1199.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-29 10:48
@@ -19901,23 +19893,23 @@
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t>2026-10-01 11:12:55</t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C735" t="inlineStr">
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
         <is>
           <t>260929AD47N1M5</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr">
+      <c r="D734" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-29 12:08, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-29 12:08
@@ -19932,23 +19924,23 @@
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t>2026-10-01 11:13:53</t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
         <is>
           <t>260929AUBFYE55</t>
         </is>
       </c>
-      <c r="D736" t="inlineStr">
+      <c r="D735" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-29 16:22, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-29 16:22
@@ -19963,23 +19955,23 @@
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t>2026-10-01 11:14:45</t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
         <is>
           <t>260930BQ5N9TWR</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr">
+      <c r="D736" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 00:40, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 00:40
@@ -19994,23 +19986,23 @@
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t>2026-10-01 11:15:30</t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
         <is>
           <t>260930CMWQB2C5</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr">
+      <c r="D737" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 09:33, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 09:33
@@ -20025,23 +20017,23 @@
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t>2026-10-01 11:16:23</t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C739" t="inlineStr">
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
         <is>
           <t>260930CPFHU6GG</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr">
+      <c r="D738" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 10:01, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 10:01
@@ -20056,23 +20048,23 @@
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t>2026-10-01 11:17:15</t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C740" t="inlineStr">
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
         <is>
           <t>260930CRD46V04</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr">
+      <c r="D739" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-30 10:35, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 10:35
@@ -20087,23 +20079,23 @@
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t>2026-10-01 11:17:59</t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
         <is>
           <t>260930CRRGE3HG</t>
         </is>
       </c>
-      <c r="D741" t="inlineStr">
+      <c r="D740" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 10:41, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 10:41
@@ -20118,23 +20110,23 @@
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t>2026-10-01 11:18:41</t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr">
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
         <is>
           <t>260930CSF92JFU</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr">
+      <c r="D741" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-30 10:54, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 10:54
@@ -20149,23 +20141,23 @@
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t>2026-10-01 11:19:47</t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
         <is>
           <t>260930CSY6B7RG</t>
         </is>
       </c>
-      <c r="D743" t="inlineStr">
+      <c r="D742" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001778+SP2-001779 (วันที่: 2026-09-30 11:03, ราคาที่ต้องออกบิล: 832.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 11:03
@@ -20180,23 +20172,23 @@
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t>2026-10-01 11:20:28</t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr">
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
         <is>
           <t>260930CT3BV45Y</t>
         </is>
       </c>
-      <c r="D744" t="inlineStr">
+      <c r="D743" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 11:05, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 11:05
@@ -20211,23 +20203,23 @@
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t>2026-10-01 11:21:19</t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
         <is>
           <t>260930CWD1HGDP</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr">
+      <c r="D744" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001607+SP2-001754 (วันที่: 2026-09-30 12:04, ราคาที่ต้องออกบิล: 794.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 12:04
@@ -20242,23 +20234,23 @@
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t>2026-10-01 11:22:03</t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
         <is>
           <t>260930CWPA53BY</t>
         </is>
       </c>
-      <c r="D746" t="inlineStr">
+      <c r="D745" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 12:10, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 12:10
@@ -20273,23 +20265,23 @@
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t>2026-10-01 11:22:50</t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C747" t="inlineStr">
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
         <is>
           <t>260930CWTKFC44</t>
         </is>
       </c>
-      <c r="D747" t="inlineStr">
+      <c r="D746" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 12:12, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 12:12
@@ -20304,23 +20296,23 @@
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t>2026-10-01 11:23:26</t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C748" t="inlineStr">
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
         <is>
           <t>260930CXRKUD4X</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr">
+      <c r="D747" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 12:29, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 12:29
@@ -20335,23 +20327,23 @@
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t>2026-10-01 11:24:12</t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C749" t="inlineStr">
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
         <is>
           <t>260930D02CVDBV</t>
         </is>
       </c>
-      <c r="D749" t="inlineStr">
+      <c r="D748" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-30 12:52, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 12:52
@@ -20366,23 +20358,23 @@
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t>2026-10-01 11:24:51</t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
         <is>
           <t>260930D263N5J1</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr">
+      <c r="D749" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 13:30, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 13:30
@@ -20397,23 +20389,23 @@
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t>2026-10-01 11:25:35</t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr">
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
         <is>
           <t>260930D2GMACGB</t>
         </is>
       </c>
-      <c r="D751" t="inlineStr">
+      <c r="D750" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 13:36, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 13:36
@@ -20428,23 +20420,23 @@
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t>2026-10-01 11:26:23</t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
         <is>
           <t>260930D4BEUF17</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr">
+      <c r="D751" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 14:09, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 14:09
@@ -20459,23 +20451,23 @@
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t>2026-10-01 11:27:36</t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
         <is>
           <t>260930D4F45W80</t>
         </is>
       </c>
-      <c r="D753" t="inlineStr">
+      <c r="D752" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: PR5-000661 (วันที่: 2026-09-30 14:11, ราคาที่ต้องออกบิล: 8602.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 14:11
@@ -20490,23 +20482,23 @@
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t>2026-10-01 11:28:22</t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
         <is>
           <t>260930D4Y48HHD</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr">
+      <c r="D753" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 14:20, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 14:20
@@ -20521,23 +20513,23 @@
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t>2026-10-01 11:29:13</t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr">
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
         <is>
           <t>260930D520TGS8</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr">
+      <c r="D754" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 14:21, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 14:21
@@ -20552,23 +20544,23 @@
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t>2026-10-01 11:30:03</t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
         <is>
           <t>260930D5NBP5R2</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr">
+      <c r="D755" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 14:32, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 14:32
@@ -20583,23 +20575,23 @@
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t>2026-10-01 11:30:51</t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C757" t="inlineStr">
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
         <is>
           <t>260930D7MDPFBE</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr">
+      <c r="D756" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 15:07, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 15:07
@@ -20614,23 +20606,23 @@
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t>2026-10-01 11:31:36</t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C758" t="inlineStr">
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
         <is>
           <t>260930D7YDJSSW</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr">
+      <c r="D757" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 15:14, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 15:14
@@ -20645,23 +20637,23 @@
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t>2026-10-01 11:32:38</t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C759" t="inlineStr">
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
         <is>
           <t>260930D84RADEG</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr">
+      <c r="D758" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP1-001420+SP1-001421+SP1-001422+SP1-001423 (วันที่: 2026-09-30 15:17, ราคาที่ต้องออกบิล: 9551.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 15:17
@@ -20676,23 +20668,23 @@
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t>2026-10-01 11:33:22</t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C760" t="inlineStr">
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
         <is>
           <t>260930D94HWSGH</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr">
+      <c r="D759" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 15:34, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 15:34
@@ -20707,23 +20699,23 @@
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t>2026-10-01 11:34:03</t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C761" t="inlineStr">
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
         <is>
           <t>260930DA47NW8F</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr">
+      <c r="D760" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-30 15:52, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 15:52
@@ -20738,23 +20730,23 @@
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t>2026-10-01 11:34:52</t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C762" t="inlineStr">
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
         <is>
           <t>260930DBBYVH84</t>
         </is>
       </c>
-      <c r="D762" t="inlineStr">
+      <c r="D761" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 16:14, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 16:14
@@ -20769,23 +20761,23 @@
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t>2026-10-01 11:35:33</t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr">
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
         <is>
           <t>260930DBUY1NKF</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr">
+      <c r="D762" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 16:23, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 16:23
@@ -20800,23 +20792,23 @@
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t>2026-10-01 11:36:04</t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C764" t="inlineStr">
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
         <is>
           <t>260930DC4DT2CY</t>
         </is>
       </c>
-      <c r="D764" t="inlineStr">
+      <c r="D763" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 16:28, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 16:28
@@ -20831,23 +20823,23 @@
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t>2026-10-01 11:37:04</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr">
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
         <is>
           <t>260930DC9TGGRK</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr">
+      <c r="D764" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP1-001445+SP1-001446+SP1-001447+SP1-001448 (วันที่: 2026-09-30 16:31, ราคาที่ต้องออกบิล: 11997.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 16:31
@@ -20862,23 +20854,23 @@
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t>2026-10-01 11:37:42</t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr">
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
         <is>
           <t>260930DE84M8KP</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr">
+      <c r="D765" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 17:06, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 17:06
@@ -20893,23 +20885,23 @@
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t>2026-10-01 11:38:23</t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C767" t="inlineStr">
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
         <is>
           <t>260930DEMDFUUH</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr">
+      <c r="D766" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 17:13, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 17:13
@@ -20924,23 +20916,23 @@
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t>2026-10-01 11:39:23</t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C768" t="inlineStr">
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
         <is>
           <t>260930DJYEBRAM</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr">
+      <c r="D767" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001803+SP2-001804+SP2-001805+SP2-001806 (วันที่: 2026-09-30 18:30, ราคาที่ต้องออกบิล: 2931.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 18:30
@@ -20955,23 +20947,23 @@
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t>2026-10-01 11:40:18</t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C769" t="inlineStr">
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
         <is>
           <t>260930DQ7SEC8A</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr">
+      <c r="D768" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-09-30 19:47, ราคาที่ต้องออกบิล: 1234.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 19:47
@@ -20986,23 +20978,23 @@
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t>2026-10-01 11:40:58</t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C770" t="inlineStr">
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
         <is>
           <t>260930DQXF5QJR</t>
         </is>
       </c>
-      <c r="D770" t="inlineStr">
+      <c r="D769" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 19:59, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 19:59
@@ -21017,23 +21009,23 @@
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t>2026-10-01 11:41:45</t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C771" t="inlineStr">
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
         <is>
           <t>260930DSQ37CAA</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr">
+      <c r="D770" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 20:31, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 20:31
@@ -21048,23 +21040,23 @@
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t>2026-10-01 11:42:38</t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C772" t="inlineStr">
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
         <is>
           <t>260930DT3V9D3U</t>
         </is>
       </c>
-      <c r="D772" t="inlineStr">
+      <c r="D771" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-09-30 20:38, ราคาที่ต้องออกบิล: 950.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 20:38
@@ -21079,23 +21071,23 @@
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t>2026-10-01 11:43:39</t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C773" t="inlineStr">
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
         <is>
           <t>260930DWC0FFR9</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr">
+      <c r="D772" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001713+SP2-001714+SP2-001715+SP2-001716 (วันที่: 2026-09-30 21:36, ราคาที่ต้องออกบิล: 1199.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 21:36
@@ -21110,23 +21102,23 @@
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t>2026-10-01 11:44:19</t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C774" t="inlineStr">
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
         <is>
           <t>260930DXU29R5B</t>
         </is>
       </c>
-      <c r="D774" t="inlineStr">
+      <c r="D773" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 22:03, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 22:03
@@ -21141,23 +21133,23 @@
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t>2026-10-01 11:44:58</t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C775" t="inlineStr">
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
         <is>
           <t>260930DYT33BP1</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr">
+      <c r="D774" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 22:20, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 22:20
@@ -21172,23 +21164,23 @@
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t>2026-10-01 11:51:01</t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C776" t="inlineStr">
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
         <is>
           <t>260930E0CK9THV</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr">
+      <c r="D775" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-09-30 22:30, ราคาที่ต้องออกบิล: 1449.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 22:30
@@ -21203,23 +21195,23 @@
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t>2026-10-01 11:51:53</t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C777" t="inlineStr">
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
         <is>
           <t>260930E0MPNP86</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr">
+      <c r="D776" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-09-30 22:35, ราคาที่ต้องออกบิล: 1017.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 22:35
@@ -21234,23 +21226,23 @@
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t>2026-10-01 11:52:39</t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C778" t="inlineStr">
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
         <is>
           <t>260930E0VAU94H</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr">
+      <c r="D777" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 22:39, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 22:39
@@ -21265,23 +21257,23 @@
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t>2026-10-01 11:53:25</t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C779" t="inlineStr">
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
         <is>
           <t>261001E2QNN8JN</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr">
+      <c r="D778" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-09-30 23:12, ราคาที่ต้องออกบิล: 955.0)
 SHOPEE เวลาสั่งซื้อ 2026-09-30 23:12
@@ -21296,23 +21288,23 @@
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t>2026-10-01 11:54:16</t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C780" t="inlineStr">
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
         <is>
           <t>261001E6J662DF</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr">
+      <c r="D779" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-10-01 00:21, ราคาที่ต้องออกบิล: 969.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 00:21
@@ -21327,23 +21319,23 @@
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t>2026-10-01 11:55:04</t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C781" t="inlineStr">
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
         <is>
           <t>261001E71XP9NF</t>
         </is>
       </c>
-      <c r="D781" t="inlineStr">
+      <c r="D780" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-10-01 00:30, ราคาที่ต้องออกบิล: 969.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 00:30
@@ -21358,23 +21350,23 @@
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t>2026-10-01 11:55:56</t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C782" t="inlineStr">
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
         <is>
           <t>261001ECSSVJ89</t>
         </is>
       </c>
-      <c r="D782" t="inlineStr">
+      <c r="D781" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-10-01 02:13, ราคาที่ต้องออกบิล: 1477.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 02:13
@@ -21389,23 +21381,23 @@
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t>2026-10-01 11:56:40</t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C783" t="inlineStr">
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
         <is>
           <t>261001ERWH7JQF</t>
         </is>
       </c>
-      <c r="D783" t="inlineStr">
+      <c r="D782" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-10-01 05:49, ราคาที่ต้องออกบิล: 969.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 05:49
@@ -21420,23 +21412,23 @@
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t>2026-10-01 11:57:25</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C784" t="inlineStr">
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
         <is>
           <t>261001EWR5RTBE</t>
         </is>
       </c>
-      <c r="D784" t="inlineStr">
+      <c r="D783" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-10-01 07:16, ราคาที่ต้องออกบิล: 1477.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 07:16
@@ -21451,23 +21443,23 @@
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t>2026-10-01 11:58:34</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C785" t="inlineStr">
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
         <is>
           <t>261001F2URJ0H3</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr">
+      <c r="D784" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-10-01 08:47, ราคาที่ต้องออกบิล: 969.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 08:47
@@ -21482,23 +21474,23 @@
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t>2026-10-01 11:59:39</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
         <is>
           <t>261001F3WXD5F0</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr">
+      <c r="D785" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not set for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-10-01 09:07, ราคาที่ต้องออกบิล: 974.0)
 SHOPEE เวลาสั่งซื้อ 2026-10-01 09:07
@@ -21514,6 +21506,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D785"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21526,6 +21519,16 @@
   </sheetPr>
   <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -23225,8 +23228,10 @@
           <t>B0183-W09-2608070001</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>18348</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>18348</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -23306,8 +23311,10 @@
           <t>B0183-W08-2608190003</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>1200</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -23392,8 +23399,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>5209</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -23422,8 +23431,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>910</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -23452,8 +23463,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>5567</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -23482,8 +23495,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>1090</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -23512,8 +23527,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E109" t="n">
-        <v>27166</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>27166</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -23542,8 +23559,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v>5452</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -23572,8 +23591,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v>5970</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -23624,8 +23645,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>2990</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -23659,8 +23682,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>5474</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>5474</t>
+        </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -23721,8 +23746,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v>9673</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>9673</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -23733,17 +23760,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-01 11:10:35</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TH2630217851490</t>
+          <t>2026-10-01 11:10:49</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2609287HFYKV3U</t>
+          <t>26092993CB5115</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23751,8 +23773,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>1449</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -23763,12 +23787,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-01 11:10:49</t>
+          <t>2026-10-01 11:11:04</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>26092993CB5115</t>
+          <t>260929A9FF4P5G</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23776,8 +23800,10 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E118" t="n">
-        <v>1017</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -23788,12 +23814,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-01 11:11:04</t>
+          <t>2026-10-01 17:58:35</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TH2630217851490</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>260929A9FF4P5G</t>
+          <t>2609287HFYKV3U</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23801,16 +23832,24 @@
           <t>TEST_MODE</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>959</v>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1449.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795: POS=1,449.00/เป้า=1,449.00 [ตรง ✅] | Total: POS=1,449.00/เป้า=1,449.00 [ตรง ✅]</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาผ่าน/All OK)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23823,6 +23862,9 @@
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -23842,6 +23884,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23852,57 +23895,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tracking</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>bill_no</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sn</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>error_category</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:58:35</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TH2630217851490</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1449.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795: POS=1,449.00/เป้า=1,449.00 [ตรง ✅] | Total: POS=1,449.00/เป้า=1,449.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Processed_Logs'!$A$1:$I$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failed_Orders'!$A$1:$D$776</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Completed_Orders'!$A$1:$C$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Processed_Logs'!$A$1:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failed_Orders'!$A$1:$D$785</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Completed_Orders'!$A$1:$C$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sheet4'!$A$1:$A$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -505,7 +505,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>261004PYNMBJ77</t>
+        </is>
+      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>MMV98ST00162100F463S00</t>
@@ -519,7 +523,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>261004Q63DF97T</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MMV98ST001621011B63S00</t>
@@ -529,7 +537,11 @@
       <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>MMV98ST001611000C73S00</t>
@@ -539,85 +551,141 @@
       <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
       <c r="B10" s="4" t="inlineStr"/>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>261004QGFRUB89</t>
+        </is>
+      </c>
       <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>261004QT6B3W6T</t>
+        </is>
+      </c>
       <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
       <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>261004QX1BTQAW</t>
+        </is>
+      </c>
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>261004R2R0Q9HS</t>
+        </is>
+      </c>
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>261004R3TD9APG</t>
+        </is>
+      </c>
       <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>261005R7HD9X0E</t>
+        </is>
+      </c>
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>261005R8GY74FG</t>
+        </is>
+      </c>
       <c r="B19" s="4" t="inlineStr"/>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>261005RFNTFJ0M</t>
+        </is>
+      </c>
       <c r="B20" s="4" t="inlineStr"/>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>261005RYAJ324R</t>
+        </is>
+      </c>
       <c r="B21" s="4" t="inlineStr"/>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
       <c r="B22" s="4" t="inlineStr"/>
       <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="inlineStr"/>
@@ -629,31 +697,51 @@
       <c r="D23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>261005S279WG28</t>
+        </is>
+      </c>
       <c r="B24" s="4" t="inlineStr"/>
       <c r="C24" s="4" t="inlineStr"/>
       <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>261005S3M1DU26</t>
+        </is>
+      </c>
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>261005S561P3G2</t>
+        </is>
+      </c>
       <c r="B26" s="4" t="inlineStr"/>
       <c r="C26" s="4" t="inlineStr"/>
       <c r="D26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
       <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="4" t="inlineStr"/>
       <c r="D27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
       <c r="B28" s="4" t="inlineStr"/>
       <c r="C28" s="4" t="inlineStr"/>
       <c r="D28" s="4" t="inlineStr"/>
@@ -1090,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -1100,7 +1188,7 @@
     <col width="15" customWidth="1" style="5" min="5" max="5"/>
     <col width="20" customWidth="1" style="5" min="6" max="6"/>
     <col width="51" customWidth="1" style="5" min="7" max="7"/>
-    <col width="18" customWidth="1" style="5" min="8" max="8"/>
+    <col width="19" customWidth="1" style="5" min="8" max="8"/>
     <col width="70" customWidth="1" style="5" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -3568,83 +3656,83 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:57:19</t>
+          <t>2026-10-02 17:57:24</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>TH2649086552223</t>
+          <t>TH261896442233P</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>261002HHRWC6MC</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>1056.0</t>
-        </is>
-      </c>
+          <t>261002HJMQ3P5U</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
+      <c r="I69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:57:24</t>
+          <t>2026-10-02 17:58:22</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>TH261896442233P</t>
+          <t>TH263149080303J</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>261002HJMQ3P5U</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr"/>
+          <t>261002HM5CG6JM</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:58:22</t>
+          <t>2026-10-02 17:59:01</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>TH263149080303J</t>
+          <t>TH268776951069O</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>261002HM5CG6JM</t>
+          <t>261002HMFAY2EQ</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3654,7 +3742,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>974.0</t>
+          <t>1056.0</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -3666,183 +3754,518 @@
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:01</t>
+          <t>2026-10-02 17:59:08</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>TH268776951069O</t>
+          <t>TH260983554839J</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>261002HMFAY2EQ</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>1056.0</t>
-        </is>
-      </c>
+          <t>261002HN2N0SB4</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
+      <c r="I72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:08</t>
+          <t>2026-10-02 17:59:39</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TH260983554839J</t>
+          <t>TH2613592229088</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>261002HN2N0SB4</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
+          <t>261002HNMRU6N2</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:39</t>
+          <t>2026-10-02 17:59:45</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>TH2613592229088</t>
+          <t>TH040697FCG04D</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>261002HNMRU6N2</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>278.0</t>
-        </is>
-      </c>
+          <t>261002HPM17BKR</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
-        </is>
-      </c>
+      <c r="I74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:45</t>
+          <t>2026-10-02 18:00:26</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>TH040697FCG04D</t>
+          <t>TH261278054656S</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>261002HPM17BKR</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
+          <t>261002HSH1MCYP</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>1603.0</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 18:00:26</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>TH261278054656S</t>
-        </is>
-      </c>
+          <t>2026-10-05 10:35:06</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr"/>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>261002HSH1MCYP</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>1603.0</t>
-        </is>
-      </c>
+          <t>261002HSQNAN0G</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HSQNAN0G ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:08</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr"/>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>261002HST6DBDD</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HST6DBDD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:09</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr"/>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>261002HTPHAVFD</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HTPHAVFD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:11</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr"/>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>261002HXGQF53W</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HXGQF53W ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:12</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr"/>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>261002HYAXPRKH</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HYAXPRKH ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:13</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr"/>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>261002J054W3CE</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J054W3CE ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:15</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr"/>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>261002J07DEMAS</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J07DEMAS ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:36:51</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>TH2649086552223</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>261002HHRWC6MC</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
           <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:37:27</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>TH266344451938Z</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>261002JEPP9507</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:38:02</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>TH269692353735Y</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:38:51</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>TH260526331025L</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>261003ND0STEU0</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>1280.0</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613: POS=1,280.00/เป้า=1,280.00 [ตรง ✅] | Total: POS=1,280.00/เป้า=1,280.00 [ตรง ✅]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I76"/>
+  <autoFilter ref="A1:I86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3853,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D776"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -24509,8 +24932,216 @@
         </is>
       </c>
     </row>
+    <row r="777">
+      <c r="A777" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:07</t>
+        </is>
+      </c>
+      <c r="B777" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C777" s="4" t="inlineStr">
+        <is>
+          <t>261002HSQNAN0G</t>
+        </is>
+      </c>
+      <c r="D777" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HSQNAN0G ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:08</t>
+        </is>
+      </c>
+      <c r="B778" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C778" s="4" t="inlineStr">
+        <is>
+          <t>261002HST6DBDD</t>
+        </is>
+      </c>
+      <c r="D778" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HST6DBDD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:10</t>
+        </is>
+      </c>
+      <c r="B779" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C779" s="4" t="inlineStr">
+        <is>
+          <t>261002HTPHAVFD</t>
+        </is>
+      </c>
+      <c r="D779" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HTPHAVFD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:11</t>
+        </is>
+      </c>
+      <c r="B780" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C780" s="4" t="inlineStr">
+        <is>
+          <t>261002HXGQF53W</t>
+        </is>
+      </c>
+      <c r="D780" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HXGQF53W ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:13</t>
+        </is>
+      </c>
+      <c r="B781" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C781" s="4" t="inlineStr">
+        <is>
+          <t>261002HYAXPRKH</t>
+        </is>
+      </c>
+      <c r="D781" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HYAXPRKH ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:14</t>
+        </is>
+      </c>
+      <c r="B782" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C782" s="4" t="inlineStr">
+        <is>
+          <t>261002J054W3CE</t>
+        </is>
+      </c>
+      <c r="D782" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J054W3CE ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:35:15</t>
+        </is>
+      </c>
+      <c r="B783" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C783" s="4" t="inlineStr">
+        <is>
+          <t>261002J07DEMAS</t>
+        </is>
+      </c>
+      <c r="D783" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J07DEMAS ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:37:59</t>
+        </is>
+      </c>
+      <c r="B784" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C784" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D784" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:38:02</t>
+        </is>
+      </c>
+      <c r="B785" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C785" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D785" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D776"/>
+  <autoFilter ref="A1:D785"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24521,7 +25152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -27592,46 +28223,46 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:57:19</t>
+          <t>2026-10-02 17:57:24</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>261002HHRWC6MC</t>
+          <t>261002HJMQ3P5U</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:57:24</t>
+          <t>2026-10-02 17:58:22</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>261002HJMQ3P5U</t>
+          <t>261002HM5CG6JM</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:58:22</t>
+          <t>2026-10-02 17:59:01</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>261002HM5CG6JM</t>
+          <t>261002HMFAY2EQ</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -27643,80 +28274,80 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:01</t>
+          <t>2026-10-02 17:59:08</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>261002HMFAY2EQ</t>
+          <t>261002HN2N0SB4</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:08</t>
+          <t>2026-10-02 17:59:39</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>261002HN2N0SB4</t>
+          <t>261002HNMRU6N2</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:39</t>
+          <t>2026-10-02 17:59:45</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>261002HNMRU6N2</t>
+          <t>261002HPM17BKR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:45</t>
+          <t>2026-10-02 18:00:26</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>261002HPM17BKR</t>
+          <t>261002HSH1MCYP</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 18:00:26</t>
+          <t>2026-10-05 10:36:51</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>261002HSH1MCYP</t>
+          <t>261002HHRWC6MC</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -27725,8 +28356,42 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:37:27</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>261002JEPP9507</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:38:51</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>261003ND0STEU0</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C188"/>
+  <autoFilter ref="A1:C190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_uat.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Processed_Logs'!$A$1:$I$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failed_Orders'!$A$1:$D$785</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Completed_Orders'!$A$1:$C$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Processed_Logs'!$A$1:$I$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Failed_Orders'!$A$1:$D$850</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Completed_Orders'!$A$1:$C$232</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sheet4'!$A$1:$A$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -405,7 +405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="5" min="1" max="1"/>
@@ -437,7 +437,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>261001FEC5SUDM</t>
+        </is>
+      </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
           <t>2609251AWCE1CK</t>
@@ -505,11 +509,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>261004PYNMBJ77</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>MMV98ST00162100F463S00</t>
@@ -523,11 +523,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>261004Q63DF97T</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MMV98ST001621011B63S00</t>
@@ -537,11 +533,7 @@
       <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>261004Q9QH1P3V</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="inlineStr"/>
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>MMV98ST001611000C73S00</t>
@@ -550,624 +542,8 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>261004QA477QPM</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>261004QDHEFM8R</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>261004QGFRUB89</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>261004QKKKN7CP</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>261004QT6B3W6T</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>261004QTYKSRBC</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>261004QX1BTQAW</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>261004R2R0Q9HS</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>261004R3TD9APG</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>261005R7HD9X0E</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>261005R8GY74FG</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>261005RFNTFJ0M</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>261005RYAJ324R</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>261005S1000PVF</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>261005S279WG28</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr"/>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>261005S3M1DU26</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>261005S561P3G2</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>261005S6S2BQR4</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>261005S7BW2KXG</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr"/>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr"/>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr"/>
-      <c r="B38" s="4" t="inlineStr"/>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="4" t="inlineStr"/>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="4" t="inlineStr"/>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="4" t="inlineStr"/>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr"/>
-      <c r="B43" s="4" t="inlineStr"/>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="4" t="inlineStr"/>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr"/>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr"/>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr"/>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr"/>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr"/>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr"/>
-      <c r="B53" s="4" t="inlineStr"/>
-      <c r="C53" s="4" t="inlineStr"/>
-      <c r="D53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="4" t="inlineStr"/>
-      <c r="C55" s="4" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr"/>
-      <c r="B56" s="4" t="inlineStr"/>
-      <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr"/>
-      <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr"/>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr"/>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr"/>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr"/>
-      <c r="B62" s="4" t="inlineStr"/>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr"/>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr"/>
-      <c r="B64" s="4" t="inlineStr"/>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr"/>
-      <c r="C65" s="4" t="inlineStr"/>
-      <c r="D65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr"/>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr"/>
-      <c r="C67" s="4" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="4" t="inlineStr"/>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr"/>
-      <c r="C69" s="4" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr"/>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr"/>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr"/>
-      <c r="C72" s="4" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr"/>
-      <c r="B74" s="4" t="inlineStr"/>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="4" t="inlineStr"/>
-      <c r="D75" s="4" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr"/>
-      <c r="B76" s="4" t="inlineStr"/>
-      <c r="C76" s="4" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr"/>
-      <c r="C78" s="4" t="inlineStr"/>
-      <c r="D78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>261002HSQNAN0G</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr"/>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>261002HST6DBDD</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr"/>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>261002HTPHAVFD</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr"/>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>261002HXGQF53W</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr"/>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>261002HYAXPRKH</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr"/>
-      <c r="C83" s="4" t="inlineStr"/>
-      <c r="D83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>261002J054W3CE</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr"/>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>261002J07DEMAS</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="4" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>261002J2RVRWU8</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr"/>
-      <c r="C86" s="4" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>261002J4KNCUXG</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr"/>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>261002J4XP7BE4</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr"/>
-      <c r="C88" s="4" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>261002J7R38VY4</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr"/>
-      <c r="C89" s="4" t="inlineStr"/>
-      <c r="D89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>261002J9J422Y3</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr"/>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D90"/>
+  <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1178,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -1239,7 +615,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:53:05</t>
@@ -1278,7 +654,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:54:20</t>
@@ -1313,7 +689,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:55:11</t>
@@ -1352,7 +728,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:55:56</t>
@@ -1387,7 +763,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:58:32</t>
@@ -1426,7 +802,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 15:59:05</t>
@@ -1465,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:00:23</t>
@@ -1500,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:02:29</t>
@@ -1539,7 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:03:12</t>
@@ -1578,7 +954,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:06:05</t>
@@ -1617,7 +993,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1" s="5">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:06:51</t>
@@ -1656,7 +1032,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1" s="5">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:07:35</t>
@@ -1695,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1" s="5">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:08:21</t>
@@ -1734,7 +1110,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1" s="5">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:15:17</t>
@@ -1773,7 +1149,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="1" s="5">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:15:48</t>
@@ -1812,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="1" s="5">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:17:25</t>
@@ -1851,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1" s="5">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:18:30</t>
@@ -1890,7 +1266,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1" s="5">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:19:06</t>
@@ -1929,7 +1305,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1" s="5">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:19:37</t>
@@ -1968,7 +1344,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1" s="5">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:20:11</t>
@@ -2007,7 +1383,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1" s="5">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:20:38</t>
@@ -2046,7 +1422,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" s="5">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:22:58</t>
@@ -2085,7 +1461,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1" s="5">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:24:01</t>
@@ -2124,7 +1500,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" s="5">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:27:08</t>
@@ -2163,7 +1539,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" s="5">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:27:50</t>
@@ -2202,7 +1578,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1" s="5">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:28:30</t>
@@ -2241,7 +1617,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" s="5">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:29:42</t>
@@ -2280,7 +1656,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" s="5">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:30:23</t>
@@ -2319,7 +1695,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" s="5">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:32:04</t>
@@ -2358,7 +1734,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" s="5">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:33:07</t>
@@ -2393,7 +1769,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1" s="5">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:34:29</t>
@@ -2432,7 +1808,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" s="5">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 16:35:44</t>
@@ -2471,7 +1847,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="1" s="5">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 17:41:00</t>
@@ -2498,7 +1874,7 @@
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr"/>
     </row>
-    <row r="35">
+    <row r="35" hidden="1" s="5">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 17:41:30</t>
@@ -2537,7 +1913,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1" s="5">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>2026-10-02 17:42:08</t>
@@ -2576,64 +1952,59 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" s="5">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:42:43</t>
+          <t>2026-10-02 17:45:35</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>TH200697EDG66F</t>
+          <t>TH262072402045S</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>261001FBHJNT5P</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+          <t>261001FFS32AXE</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2112.0</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Order skipped, CP/DC not set for SKU: SP4-000196 (วันที่: 2026-10-01 11:23, ราคาที่ต้องออกบิล: 305.0)
-SHOPEE เวลาสั่งซื้อ 2026-10-01 11:23
-SP4-000196 Epson EPS RB S015582/S015306 LQ630 หมึกพิมพ์ (SP4-000196)
-ยิงขายขึ้น 360.00 บาท
-ลูกค้าซื้อราคา 305.00 บาท
-ขอวิธีปรับราคาครับ
-💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 305.00 บาท พอดีเป๊ะ:
-   • แนะนำ: 'DC2609300024' (ส่วนลด 55.00 บาท)
-   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
- (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=2,112.00/เป้า=2,112.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" hidden="1" s="5">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:44:55</t>
+          <t>2026-10-02 17:45:41</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TH250697EE4V4A</t>
+          <t>TH262300086931C</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>261001FEC5SUDM</t>
+          <t>261001FHM1BSGG</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
@@ -2641,127 +2012,131 @@
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Thread has been terminated during select_sale_type (ด่านที่ติด: เริ่มรัน)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" hidden="1" s="5">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:45:35</t>
+          <t>2026-10-02 17:45:48</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>TH262072402045S</t>
+          <t>TH2639597108641</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>261001FFS32AXE</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>2112.0</t>
-        </is>
-      </c>
+          <t>261001FJGE88WY</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=2,112.00/เป้า=2,112.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+      <c r="I39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" hidden="1" s="5">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:45:41</t>
+          <t>2026-10-02 17:46:27</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>TH262300086931C</t>
+          <t>TH262862501680O</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>261001FHM1BSGG</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
+          <t>261001FJH0DC5S</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" hidden="1" s="5">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:45:48</t>
+          <t>2026-10-02 17:47:14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>TH2639597108641</t>
+          <t>TH267562033596Z</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>261001FJGE88WY</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
+          <t>261001FNX3QHKT</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>9673.0</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423: POS=9,673.00/เป้า=9,673.00 [ตรง ✅] | Total: POS=9,673.00/เป้า=9,673.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" hidden="1" s="5">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:46:27</t>
+          <t>2026-10-02 17:47:52</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>TH262862501680O</t>
+          <t>TH266356362187S</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>261001FJH0DC5S</t>
+          <t>261001FSKPY1CK</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2787,20 +2162,20 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1" s="5">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:47:14</t>
+          <t>2026-10-02 17:48:20</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>TH267562033596Z</t>
+          <t>TH2603840642214</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>261001FNX3QHKT</t>
+          <t>261001FX5EERNK</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2810,7 +2185,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>9673.0</t>
+          <t>1446.0</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -2822,24 +2197,24 @@
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423: POS=9,673.00/เป้า=9,673.00 [ตรง ✅] | Total: POS=9,673.00/เป้า=9,673.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+          <t>SP1-001210: POS=1,446.00/เป้า=1,446.00 [ตรง ✅] | Total: POS=1,446.00/เป้า=1,446.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" hidden="1" s="5">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:47:52</t>
+          <t>2026-10-02 17:48:54</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>TH266356362187S</t>
+          <t>TH012897EE4V8B</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>261001FSKPY1CK</t>
+          <t>261001F6QM152N</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2849,7 +2224,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>1056.0</t>
+          <t>1603.0</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -2861,24 +2236,24 @@
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
+          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" hidden="1" s="5">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:48:20</t>
+          <t>2026-10-02 17:49:28</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>TH2603840642214</t>
+          <t>TH266659582021T</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>261001FX5EERNK</t>
+          <t>261001G123D1HD</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2888,7 +2263,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1446.0</t>
+          <t>1056.0</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -2900,230 +2275,206 @@
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>SP1-001210: POS=1,446.00/เป้า=1,446.00 [ตรง ✅] | Total: POS=1,446.00/เป้า=1,446.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" hidden="1" s="5">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:48:54</t>
+          <t>2026-10-02 17:49:33</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>TH012897EE4V8B</t>
+          <t>TH268819274686H</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>261001F6QM152N</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>1603.0</t>
-        </is>
-      </c>
+          <t>261001G1H15APF</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+      <c r="I46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" hidden="1" s="5">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:49:28</t>
+          <t>2026-10-02 17:49:39</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>TH266659582021T</t>
+          <t>TH2611946323525</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>261001G123D1HD</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>1056.0</t>
-        </is>
-      </c>
+          <t>261001G29UJPK7</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+      <c r="I47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" hidden="1" s="5">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:49:33</t>
+          <t>2026-10-02 17:50:13</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>TH268819274686H</t>
+          <t>TH040297ECNA6C0</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>261001G1H15APF</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr"/>
+          <t>261001G2Q41G2D</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49">
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" hidden="1" s="5">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:49:39</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>TH2611946323525</t>
-        </is>
-      </c>
+          <t>2026-10-02 17:51:13</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr"/>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>261001G29UJPK7</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
+          <t>261001G5NXM272</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>986.0</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | SV0-000101: POS=17.00/เป้า=17.00 [ตรง ✅] | Total: POS=986.00/เป้า=986.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" hidden="1" s="5">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:50:13</t>
+          <t>2026-10-02 17:51:18</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TH040297ECNA6C0</t>
+          <t>TH267100778887E</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>261001G2Q41G2D</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>1056.0</t>
-        </is>
-      </c>
+          <t>261001G6EP4W4P</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+      <c r="I50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" hidden="1" s="5">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:13</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr"/>
+          <t>2026-10-02 17:51:24</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>TH2694075198235</t>
+        </is>
+      </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>261001G5NXM272</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>986.0</t>
-        </is>
-      </c>
+          <t>261001G8KTNVY5</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | SV0-000101: POS=17.00/เป้า=17.00 [ตรง ✅] | Total: POS=986.00/เป้า=986.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+      <c r="I51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" hidden="1" s="5">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:18</t>
+          <t>2026-10-02 17:51:29</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>TH267100778887E</t>
+          <t>TH268087901234G</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>261001G6EP4W4P</t>
+          <t>261001G8S96PN0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -3137,113 +2488,125 @@
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr"/>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" s="5">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:24</t>
+          <t>2026-10-02 17:51:55</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>TH2694075198235</t>
+          <t>TH261397034801Z</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>261001G8KTNVY5</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
+          <t>261001G972Q8MT</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" hidden="1" s="5">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:29</t>
+          <t>2026-10-02 17:52:26</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TH268087901234G</t>
+          <t>TH266534219691L</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>261001G8S96PN0</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
+          <t>261001G9JTGPDY</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" hidden="1" s="5">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:55</t>
+          <t>2026-10-02 17:52:31</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>TH261397034801Z</t>
+          <t>TH266686158756L</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>261001G972Q8MT</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>278.0</t>
-        </is>
-      </c>
+          <t>261001GAM4NGYG</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+      <c r="I55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" hidden="1" s="5">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:52:26</t>
+          <t>2026-10-02 17:53:06</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>TH266534219691L</t>
+          <t>TH261941186388X</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>261001G9JTGPDY</t>
+          <t>261001GAWSNMEN</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3269,47 +2632,59 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" s="5">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:52:31</t>
+          <t>2026-10-02 17:53:51</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>TH266686158756L</t>
+          <t>TH200497EBQX5B0</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>261001GAM4NGYG</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
+          <t>261001GB9FJ3J3</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" s="5">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:53:06</t>
+          <t>2026-10-02 17:54:29</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>TH261941186388X</t>
+          <t>TH266706399687S</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>261001GAWSNMEN</t>
+          <t>261001GBFNUHHY</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3335,59 +2710,47 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" s="5">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:53:51</t>
+          <t>2026-10-02 17:54:34</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>TH200497EBQX5B0</t>
+          <t>TH267907824540P</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>261001GB9FJ3J3</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>974.0</t>
-        </is>
-      </c>
+          <t>261001GF2S0119</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+      <c r="I59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" hidden="1" s="5">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:54:29</t>
+          <t>2026-10-02 17:55:04</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>TH266706399687S</t>
+          <t>TH011197EDS28A</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>261001GBFNUHHY</t>
+          <t>261001GGR265EJ</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3397,7 +2760,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>1056.0</t>
+          <t>2460.0</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -3409,24 +2772,24 @@
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>SP4-000076: POS=590.00/เป้า=590.00 [ตรง ✅] | SV0-000101: POS=100.00/เป้า=100.00 [ตรง ✅] | Total: POS=2,460.00/เป้า=2,460.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" hidden="1" s="5">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:54:34</t>
+          <t>2026-10-02 17:55:10</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>TH267907824540P</t>
+          <t>TH269862831768F</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>261001GF2S0119</t>
+          <t>261001GJ20XFAV</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
@@ -3440,20 +2803,20 @@
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="4" t="inlineStr"/>
     </row>
-    <row r="62">
+    <row r="62" hidden="1" s="5">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:04</t>
+          <t>2026-10-02 17:55:36</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>TH011197EDS28A</t>
+          <t>TH272197ECAH1F</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>261001GGR265EJ</t>
+          <t>261002GJPUHERY</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3463,7 +2826,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2460.0</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -3475,24 +2838,24 @@
       <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>SP4-000076: POS=590.00/เป้า=590.00 [ตรง ✅] | SV0-000101: POS=100.00/เป้า=100.00 [ตรง ✅] | Total: POS=2,460.00/เป้า=2,460.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" hidden="1" s="5">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:10</t>
+          <t>2026-10-02 17:55:41</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>TH269862831768F</t>
+          <t>TH269873536006J</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>261001GJ20XFAV</t>
+          <t>261002GPC64FPW</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -3506,59 +2869,47 @@
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1" s="5">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:36</t>
+          <t>2026-10-02 17:55:47</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>TH272197ECAH1F</t>
+          <t>TH263829155584K</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>261002GJPUHERY</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>278.0</t>
-        </is>
-      </c>
+          <t>261002GTF4M38S</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+      <c r="I64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" hidden="1" s="5">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:41</t>
+          <t>2026-10-02 17:55:52</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>TH269873536006J</t>
+          <t>TH261870684425P</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>261002GPC64FPW</t>
+          <t>261002HBHRV5W1</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -3572,20 +2923,20 @@
       <c r="H65" s="4" t="inlineStr"/>
       <c r="I65" s="4" t="inlineStr"/>
     </row>
-    <row r="66">
+    <row r="66" hidden="1" s="5">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:47</t>
+          <t>2026-10-02 17:55:58</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>TH263829155584K</t>
+          <t>TH260641203403N</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>261002GTF4M38S</t>
+          <t>261002HHF4GR6G</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
@@ -3599,20 +2950,20 @@
       <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr"/>
     </row>
-    <row r="67">
+    <row r="67" hidden="1" s="5">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:52</t>
+          <t>2026-10-02 17:57:24</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>TH261870684425P</t>
+          <t>TH261896442233P</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>261002HBHRV5W1</t>
+          <t>261002HJMQ3P5U</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -3626,113 +2977,125 @@
       <c r="H67" s="4" t="inlineStr"/>
       <c r="I67" s="4" t="inlineStr"/>
     </row>
-    <row r="68">
+    <row r="68" hidden="1" s="5">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:55:58</t>
+          <t>2026-10-02 17:58:22</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>TH260641203403N</t>
+          <t>TH263149080303J</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>261002HHF4GR6G</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
+          <t>261002HM5CG6JM</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" hidden="1" s="5">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:57:24</t>
+          <t>2026-10-02 17:59:01</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>TH261896442233P</t>
+          <t>TH268776951069O</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>261002HJMQ3P5U</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr"/>
+          <t>261002HMFAY2EQ</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70">
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" hidden="1" s="5">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:58:22</t>
+          <t>2026-10-02 17:59:08</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>TH263149080303J</t>
+          <t>TH260983554839J</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>261002HM5CG6JM</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>TEST_MODE</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>974.0</t>
-        </is>
-      </c>
+          <t>261002HN2N0SB4</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+      <c r="I70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71" hidden="1" s="5">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:01</t>
+          <t>2026-10-02 17:59:39</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>TH268776951069O</t>
+          <t>TH2613592229088</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>261002HMFAY2EQ</t>
+          <t>261002HNMRU6N2</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3742,7 +3105,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1056.0</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -3754,24 +3117,24 @@
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" hidden="1" s="5">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:08</t>
+          <t>2026-10-02 17:59:45</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>TH260983554839J</t>
+          <t>TH040697FCG04D</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>261002HN2N0SB4</t>
+          <t>261002HPM17BKR</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -3785,20 +3148,20 @@
       <c r="H72" s="4" t="inlineStr"/>
       <c r="I72" s="4" t="inlineStr"/>
     </row>
-    <row r="73">
+    <row r="73" hidden="1" s="5">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:39</t>
+          <t>2026-10-02 18:00:26</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TH2613592229088</t>
+          <t>TH261278054656S</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>261002HNMRU6N2</t>
+          <t>261002HSH1MCYP</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3808,7 +3171,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>278.0</t>
+          <t>1603.0</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr"/>
@@ -3820,51 +3183,63 @@
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" s="5">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:45</t>
+          <t>2026-10-05 15:08:57</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>TH040697FCG04D</t>
+          <t>TH260526331025L</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>261002HPM17BKR</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
+          <t>261003ND0STEU0</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>1280.0</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613: POS=1,280.00/เป้า=1,280.00 [ตรง ✅] | Total: POS=1,280.00/เป้า=1,280.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" s="5">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 18:00:26</t>
+          <t>2026-10-05 15:09:57</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>TH261278054656S</t>
+          <t>TH210197RQXN6A</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>261002HSH1MCYP</t>
+          <t>261004PYNMBJ77</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3874,7 +3249,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1603.0</t>
+          <t>1446.0</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr"/>
@@ -3886,241 +3261,297 @@
       <c r="H75" s="4" t="inlineStr"/>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>SP1-001113: POS=1,603.00/เป้า=1,603.00 [ตรง ✅] | Total: POS=1,603.00/เป้า=1,603.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+          <t>SP1-001210: POS=1,446.00/เป้า=1,446.00 [ตรง ✅] | Total: POS=1,446.00/เป้า=1,446.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" s="5">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:06</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:10:26</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>TH040297RQEN7B</t>
+        </is>
+      </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>261002HSQNAN0G</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="inlineStr"/>
+          <t>261004Q63DF97T</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HSQNAN0G ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" s="5">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:08</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:12:34</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>TH010497RQ0F2A</t>
+        </is>
+      </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>261002HST6DBDD</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
+          <t>261004QGFRUB89</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>978.0</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HST6DBDD ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | SV0-000101: POS=4.00/เป้า=4.00 [ตรง ✅] | Total: POS=978.00/เป้า=978.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="5">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:09</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:13:48</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>TH263188231328P</t>
+        </is>
+      </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>261002HTPHAVFD</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="4" t="inlineStr"/>
+          <t>261004QT6B3W6T</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>1280.0</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HTPHAVFD ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613: POS=1,280.00/เป้า=1,280.00 [ตรง ✅] | Total: POS=1,280.00/เป้า=1,280.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" s="5">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:11</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:15:10</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>TH260823806177J</t>
+        </is>
+      </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>261002HXGQF53W</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
+          <t>261004QX1BTQAW</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>1477.0</t>
+        </is>
+      </c>
       <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HXGQF53W ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795: POS=1,477.00/เป้า=1,477.00 [ตรง ✅] | Total: POS=1,477.00/เป้า=1,477.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" s="5">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:12</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:15:57</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>TH261883964918Y</t>
+        </is>
+      </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>261002HYAXPRKH</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
+          <t>261004R2R0Q9HS</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>969.0</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HYAXPRKH ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | Total: POS=969.00/เป้า=969.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" s="5">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:13</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:16:39</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>TH261914062630B</t>
+        </is>
+      </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>261002J054W3CE</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr"/>
+          <t>261004R3TD9APG</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>986.0</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr"/>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J054W3CE ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | SV0-000101: POS=17.00/เป้า=17.00 [ตรง ✅] | Total: POS=986.00/เป้า=986.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" s="5">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:35:15</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr"/>
+          <t>2026-10-05 15:17:21</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>TH264930486571I</t>
+        </is>
+      </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>261002J07DEMAS</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
+          <t>261005R7HD9X0E</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>ORDER_NOT_FOUND</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J07DEMAS ในไฟล์นำเข้า (Export File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" s="5">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:36:51</t>
+          <t>2026-10-05 15:18:10</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TH2649086552223</t>
+          <t>TH260494313856P</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>261002HHRWC6MC</t>
+          <t>261005R8GY74FG</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4130,7 +3561,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>1056.0</t>
+          <t>979.0</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
@@ -4142,24 +3573,24 @@
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | SV0-000101: POS=5.00/เป้า=5.00 [ตรง ✅] | Total: POS=979.00/เป้า=979.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" s="5">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:37:27</t>
+          <t>2026-10-05 15:18:49</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>TH266344451938Z</t>
+          <t>TH2689542979852</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>261002JEPP9507</t>
+          <t>261005RFNTFJ0M</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4169,7 +3600,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>1056.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr"/>
@@ -4181,64 +3612,63 @@
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755: POS=1,056.00/เป้า=1,056.00 [ตรง ✅] | Total: POS=1,056.00/เป้า=1,056.00 [ตรง ✅]</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" s="5">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:38:02</t>
+          <t>2026-10-05 15:19:28</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TH269692353735Y</t>
+          <t>TH264015293335T</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>261003K6J8B8H5</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
+          <t>261005RYAJ324R</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>1948.0</t>
+        </is>
+      </c>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>PRICE_MISMATCH</t>
-        </is>
-      </c>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr"/>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
-SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
-SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
-ยิงขายขึ้น 1,240.00 บาท
-ลูกค้าซื้อราคา 993.00 บาท
-ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=1,948.00/เป้า=1,948.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" s="5">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:38:51</t>
+          <t>2026-10-05 15:21:07</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>TH260526331025L</t>
+          <t>TH264417509310R</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>261003ND0STEU0</t>
+          <t>261005S279WG28</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4248,7 +3678,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>1280.0</t>
+          <t>974.0</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -4260,12 +3690,1223 @@
       <c r="H86" s="4" t="inlineStr"/>
       <c r="I86" s="4" t="inlineStr">
         <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" s="5">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:21:50</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>TH267571526722H</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>261005S2KKTMH7</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>978.0</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | SV0-000101: POS=4.00/เป้า=4.00 [ตรง ✅] | Total: POS=978.00/เป้า=978.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" s="5">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:22:37</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>TH262683626675D</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>261005S3M1DU26</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>1022.0</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | SV0-000101: POS=53.00/เป้า=53.00 [ตรง ✅] | Total: POS=1,022.00/เป้า=1,022.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" s="5">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:23:14</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>TH264514920296C</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>261005S561P3G2</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>590.0</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000076: POS=590.00/เป้า=590.00 [ตรง ✅] | Total: POS=590.00/เป้า=590.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="5">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:25:45</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>TH266794741296R</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>261005S9MH5YJR</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" s="5">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:26:30</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>TH2605181730048</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>261005SAA9BT7C</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=139.00/เป้า=139.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" s="5">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:27:31</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>TH2695679443409</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>261005SAJXUJYG</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=278.00/เป้า=278.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" s="5">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:28:22</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr"/>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>261005SB6KAGSA</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>3031.0</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>SP1-001378: POS=3,031.00/เป้า=3,031.00 [ตรง ✅] | Total: POS=3,031.00/เป้า=3,031.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" s="5">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:29:17</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>TH264144782340O</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>261005SCWY7TRW</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>695.0</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=695.00/เป้า=695.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" s="5">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:30:55</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>TH262596265804E</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>261005SEX8B805</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>1280.0</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
           <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613: POS=1,280.00/เป้า=1,280.00 [ตรง ✅] | Total: POS=1,280.00/เป้า=1,280.00 [ตรง ✅]</t>
         </is>
       </c>
     </row>
+    <row r="96" s="5">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:31:37</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>TH261168259391Q</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>261005SF9VA8TD</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | Total: POS=974.00/เป้า=974.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" s="5">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32:19</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>TH269244538184F</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>261005SGFV6AYU</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>810.0</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000241: POS=405.00/เป้า=405.00 [ตรง ✅] | Total: POS=810.00/เป้า=810.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" s="5">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33:28</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>TH263590119777I</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>261005SHVHRU6Q</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>1943.0</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | Total: POS=1,943.00/เป้า=1,943.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" s="5">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:34:48</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr"/>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>261005SNEAWNNV</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>1390.0</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=1,390.00/เป้า=1,390.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" s="5">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:36:02</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr"/>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>261005SNTUDA6S</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>834.0</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=834.00/เป้า=834.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" s="5">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:37:04</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr"/>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>261005SPK3PU2U</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>1011.0</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848: POS=969.00/เป้า=969.00 [ตรง ✅] | SV0-000101: POS=42.00/เป้า=42.00 [ตรง ✅] | Total: POS=1,011.00/เป้า=1,011.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" s="5">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:37:32</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr"/>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>261005SRV913UH</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>1390.0</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=1,390.00/เป้า=1,390.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="5">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:38:02</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr"/>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>261005SRV913UJ</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>1390.0</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>SP4-000302: POS=139.00/เป้า=139.00 [ตรง ✅] | Total: POS=1,390.00/เป้า=1,390.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" s="5">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:38:50</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr"/>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>261005SSG63N90</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" s="5">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:43:41</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>TH2658895810139</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>261005SKFS5G2H</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106" s="5">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:46:48</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>TH2671437894410</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107" s="5">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:04:51</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>261001FEC5SUDM</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261001FEC5SUDM ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" s="5">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:05:47</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>TH269692353735Y</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" s="5">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:07:31</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>TH2678061139540</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" s="5">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:08:11</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>TH264839607880D</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" s="5">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:08:49</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>TH2683768858100</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" s="5">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:09:55</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>TH261542533974S</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>2304.0</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598: POS=974.00/เป้า=974.00 [ตรง ✅] | SP2-001748+SP2-001615+SP2-001616+SP2-001617: POS=1,330.00/เป้า=1,330.00 [ตรง ✅] | Total: POS=2,304.00/เป้า=2,304.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" s="5">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:10:33</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>TH262693129229L</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" s="5">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:11:08</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>TH260904918151Y</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" s="5">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:11:49</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>TH263748303054V</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>261005S7DP9M25</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" s="5">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:12:29</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>TH260074332771N</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>261005SER9K7CC</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755: POS=993.00/เป้า=993.00 [ตรง ✅] | Total: POS=993.00/เป้า=993.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" s="5">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:23:23</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>TH2649086552223</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>261002HHRWC6MC</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118" s="5">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:24:10</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>TH267945272702H</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119" s="5">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:24:47</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>TH266344451938Z</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>261002JEPP9507</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>1056.0</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
+  <autoFilter ref="A1:I119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4276,7 +4917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -25140,8 +25781,1726 @@
         </is>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:41:01</t>
+        </is>
+      </c>
+      <c r="B786" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C786" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D786" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:41:06</t>
+        </is>
+      </c>
+      <c r="B787" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C787" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D787" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:41:37</t>
+        </is>
+      </c>
+      <c r="B788" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C788" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D788" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:19, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:19
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:41:41</t>
+        </is>
+      </c>
+      <c r="B789" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C789" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D789" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:19, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:19
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:42:12</t>
+        </is>
+      </c>
+      <c r="B790" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C790" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D790" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 16:20, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 16:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:42:16</t>
+        </is>
+      </c>
+      <c r="B791" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C791" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D791" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 16:20, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 16:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:43:46</t>
+        </is>
+      </c>
+      <c r="B792" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C792" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D792" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 18:08, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 18:08
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:43:50</t>
+        </is>
+      </c>
+      <c r="B793" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C793" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D793" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 18:08, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 18:08
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:45:21</t>
+        </is>
+      </c>
+      <c r="B794" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C794" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="D794" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 20:20, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 20:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:45:26</t>
+        </is>
+      </c>
+      <c r="B795" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C795" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="D795" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 20:20, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 20:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:50:12</t>
+        </is>
+      </c>
+      <c r="B796" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C796" s="4" t="inlineStr">
+        <is>
+          <t>261005RFNTFJ0M</t>
+        </is>
+      </c>
+      <c r="D796" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 02:31, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 02:31
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:50:16</t>
+        </is>
+      </c>
+      <c r="B797" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C797" s="4" t="inlineStr">
+        <is>
+          <t>261005RFNTFJ0M</t>
+        </is>
+      </c>
+      <c r="D797" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 02:31, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 02:31
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:52:18</t>
+        </is>
+      </c>
+      <c r="B798" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C798" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D798" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ (แบบคู่ผสม):
+   • คูปองเริ่มต้นที่ติดมากับสินค้า: 'CP2609290081'
+   • คูปองที่ต้องเลือกเพิ่ม: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • รหัสรวมที่แนะนำ: 'CP2609290081 DC2609290042'
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:52:22</t>
+        </is>
+      </c>
+      <c r="B799" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C799" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D799" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ (แบบคู่ผสม):
+   • คูปองเริ่มต้นที่ติดมากับสินค้า: 'CP2609290081'
+   • คูปองที่ต้องเลือกเพิ่ม: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • รหัสรวมที่แนะนำ: 'CP2609290081 DC2609290042'
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:32:37</t>
+        </is>
+      </c>
+      <c r="B800" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C800" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
+      <c r="D800" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:24, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:24
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:32:40</t>
+        </is>
+      </c>
+      <c r="B801" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C801" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
+      <c r="D801" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:24, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:24
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:28</t>
+        </is>
+      </c>
+      <c r="B802" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C802" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
+      <c r="D802" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:35, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:35
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:31</t>
+        </is>
+      </c>
+      <c r="B803" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C803" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
+      <c r="D803" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:35, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:35
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:41</t>
+        </is>
+      </c>
+      <c r="B804" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C804" s="4" t="inlineStr">
+        <is>
+          <t>261002HSQNAN0G</t>
+        </is>
+      </c>
+      <c r="D804" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HSQNAN0G ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:43</t>
+        </is>
+      </c>
+      <c r="B805" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C805" s="4" t="inlineStr">
+        <is>
+          <t>261002HST6DBDD</t>
+        </is>
+      </c>
+      <c r="D805" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HST6DBDD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:44</t>
+        </is>
+      </c>
+      <c r="B806" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C806" s="4" t="inlineStr">
+        <is>
+          <t>261002HTPHAVFD</t>
+        </is>
+      </c>
+      <c r="D806" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HTPHAVFD ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:46</t>
+        </is>
+      </c>
+      <c r="B807" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C807" s="4" t="inlineStr">
+        <is>
+          <t>261002HXGQF53W</t>
+        </is>
+      </c>
+      <c r="D807" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HXGQF53W ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:47</t>
+        </is>
+      </c>
+      <c r="B808" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C808" s="4" t="inlineStr">
+        <is>
+          <t>261002HYAXPRKH</t>
+        </is>
+      </c>
+      <c r="D808" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002HYAXPRKH ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:49</t>
+        </is>
+      </c>
+      <c r="B809" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C809" s="4" t="inlineStr">
+        <is>
+          <t>261002J054W3CE</t>
+        </is>
+      </c>
+      <c r="D809" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J054W3CE ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:50</t>
+        </is>
+      </c>
+      <c r="B810" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C810" s="4" t="inlineStr">
+        <is>
+          <t>261002J07DEMAS</t>
+        </is>
+      </c>
+      <c r="D810" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J07DEMAS ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:52</t>
+        </is>
+      </c>
+      <c r="B811" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C811" s="4" t="inlineStr">
+        <is>
+          <t>261002J2RVRWU8</t>
+        </is>
+      </c>
+      <c r="D811" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J2RVRWU8 ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:54</t>
+        </is>
+      </c>
+      <c r="B812" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C812" s="4" t="inlineStr">
+        <is>
+          <t>261002J4KNCUXG</t>
+        </is>
+      </c>
+      <c r="D812" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J4KNCUXG ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:55</t>
+        </is>
+      </c>
+      <c r="B813" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C813" s="4" t="inlineStr">
+        <is>
+          <t>261002J4XP7BE4</t>
+        </is>
+      </c>
+      <c r="D813" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J4XP7BE4 ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:57</t>
+        </is>
+      </c>
+      <c r="B814" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C814" s="4" t="inlineStr">
+        <is>
+          <t>261002J7R38VY4</t>
+        </is>
+      </c>
+      <c r="D814" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J7R38VY4 ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:33:58</t>
+        </is>
+      </c>
+      <c r="B815" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C815" s="4" t="inlineStr">
+        <is>
+          <t>261002J9J422Y3</t>
+        </is>
+      </c>
+      <c r="D815" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261002J9J422Y3 ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:36:13</t>
+        </is>
+      </c>
+      <c r="B816" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C816" s="4" t="inlineStr">
+        <is>
+          <t>261001FBHJNT5P</t>
+        </is>
+      </c>
+      <c r="D816" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261001FBHJNT5P ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:36:44</t>
+        </is>
+      </c>
+      <c r="B817" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C817" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D817" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:36:47</t>
+        </is>
+      </c>
+      <c r="B818" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C818" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D818" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:37:23</t>
+        </is>
+      </c>
+      <c r="B819" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C819" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D819" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:37:24</t>
+        </is>
+      </c>
+      <c r="B820" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C820" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D820" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:37:42</t>
+        </is>
+      </c>
+      <c r="B821" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C821" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D821" s="4" t="inlineStr">
+        <is>
+          <t>ไม่พบออเดอร์ 261004QDHEFM8R ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:54:48</t>
+        </is>
+      </c>
+      <c r="B822" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C822" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D822" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:54:51</t>
+        </is>
+      </c>
+      <c r="B823" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C823" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D823" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:57:59</t>
+        </is>
+      </c>
+      <c r="B824" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C824" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D824" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:58:03</t>
+        </is>
+      </c>
+      <c r="B825" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C825" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D825" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:58:37</t>
+        </is>
+      </c>
+      <c r="B826" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C826" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D826" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:19
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:58:40</t>
+        </is>
+      </c>
+      <c r="B827" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C827" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D827" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:19
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:59:15</t>
+        </is>
+      </c>
+      <c r="B828" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C828" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D828" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 16:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:59:18</t>
+        </is>
+      </c>
+      <c r="B829" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C829" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D829" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 16:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00:38</t>
+        </is>
+      </c>
+      <c r="B830" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C830" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D830" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 18:08
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00:41</t>
+        </is>
+      </c>
+      <c r="B831" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C831" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D831" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 18:08
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:02:06</t>
+        </is>
+      </c>
+      <c r="B832" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C832" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="D832" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 20:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:02:09</t>
+        </is>
+      </c>
+      <c r="B833" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C833" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="D833" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-04 20:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:06:43</t>
+        </is>
+      </c>
+      <c r="B834" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C834" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D834" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:06:46</t>
+        </is>
+      </c>
+      <c r="B835" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C835" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D835" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, ราคาหลังปรับไม่ตรงตามเป้าหมายสำหรับ SKU:
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ปรับราคา/ใส่คูปองสำเร็จ (จบ process ปรับราคา))</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:58:16</t>
+        </is>
+      </c>
+      <c r="B836" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C836" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D836" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+(มี SKU ใน CP_data แล้ว แต่ CP ใน Excel กับหน้า SMCO ไม่ตรงกัน:
+  • ใน cp_data.xlsx ระบุ: CP2609290081 DC2609290042
+  • บนหน้า SMCO มี: DC2609140009, DC2609170011, DC2609220003, DC2609290042)
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ (แบบคู่ผสม):
+   • คูปองเริ่มต้นที่ติดมากับสินค้า: 'CP2609290081'
+   • คูปองที่ต้องเลือกเพิ่ม: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • รหัสรวมที่แนะนำ: 'CP2609290081 DC2609290042'
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:14:04</t>
+        </is>
+      </c>
+      <c r="B837" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C837" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D837" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+(มี SKU ใน CP_data แล้ว แต่ CP ใน Excel กับหน้า SMCO ไม่ตรงกัน:
+  • ใน cp_data.xlsx ระบุ: CP2609290081 DC2609290042
+  • บนหน้า SMCO มี: DC2609140009, DC2609170011, DC2609220003, DC2609290042)
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ (แบบคู่ผสม):
+   • คูปองเริ่มต้นที่ติดมากับสินค้า: 'CP2609290081'
+   • คูปองที่ต้องเลือกเพิ่ม: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • รหัสรวมที่แนะนำ: 'CP2609290081 DC2609290042'
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:52:32</t>
+        </is>
+      </c>
+      <c r="B838" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C838" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D838" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ:
+   • แนะนำ: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:08:14</t>
+        </is>
+      </c>
+      <c r="B839" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C839" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="D839" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-03 00:04, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-03 00:04
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:10:55</t>
+        </is>
+      </c>
+      <c r="B840" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C840" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="D840" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:11:22</t>
+        </is>
+      </c>
+      <c r="B841" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C841" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="D841" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 15:19, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 15:19
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:11:50</t>
+        </is>
+      </c>
+      <c r="B842" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C842" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="D842" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 16:20, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 16:20
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:13:02</t>
+        </is>
+      </c>
+      <c r="B843" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C843" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="D843" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-04 18:08, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-04 18:08
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:20:24</t>
+        </is>
+      </c>
+      <c r="B844" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C844" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="D844" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001748+SP2-001615+SP2-001616+SP2-001617 (วันที่: 2026-10-05 07:41, ราคาที่ต้องออกบิล: 1330.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 07:41
+SP2-001748+SP2-001615+SP2-001616+SP2-001617 HP หมึกพิมพ์สำหรับปริ้นเตอร์อิงค์เจ็ทรุ่น GT53BKXL + GT52 C / M / Y และ PACK 4 สี
+ยิงขายขึ้น 1,490.00 บาท
+ลูกค้าซื้อราคา 1,330.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 1,330.00 บาท พอดีเป๊ะ:
+   • แนะนำ: 'DC2609290042' (ส่วนลด 160.00 บาท)
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:23:44</t>
+        </is>
+      </c>
+      <c r="B845" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C845" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
+      <c r="D845" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:24, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:24
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:24:25</t>
+        </is>
+      </c>
+      <c r="B846" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C846" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
+      <c r="D846" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:35, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:35
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:25:13</t>
+        </is>
+      </c>
+      <c r="B847" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C847" s="4" t="inlineStr">
+        <is>
+          <t>261005S7DP9M25</t>
+        </is>
+      </c>
+      <c r="D847" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 09:36, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 09:36
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:29:45</t>
+        </is>
+      </c>
+      <c r="B848" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C848" s="4" t="inlineStr">
+        <is>
+          <t>261005SER9K7CC</t>
+        </is>
+      </c>
+      <c r="D848" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 11:47, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 11:47
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:34:01</t>
+        </is>
+      </c>
+      <c r="B849" s="4" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C849" s="4" t="inlineStr">
+        <is>
+          <t>261005SKFS5G2H</t>
+        </is>
+      </c>
+      <c r="D849" s="4" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: SP2-001753+SP2-001755 (วันที่: 2026-10-05 13:12, ราคาที่ต้องออกบิล: 993.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-05 13:12
+SP2-001753+SP2-001755 CANON ตลับหมึกรุ่น  PG-47 BK / CANON Ink CL-57 CO และ PACK คู่ 2 สี
+ยิงขายขึ้น 1,240.00 บาท
+ลูกค้าซื้อราคา 993.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:04:52</t>
+        </is>
+      </c>
+      <c r="B850" s="4" t="inlineStr">
+        <is>
+          <t>ORDER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C850" s="4" t="inlineStr">
+        <is>
+          <t>261001FEC5SUDM</t>
+        </is>
+      </c>
+      <c r="D850" s="4" t="inlineStr">
+        <is>
+          <t>Error in order_search (ValueError): ไม่พบออเดอร์ 261001FEC5SUDM ในไฟล์นำเข้า (Export File)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D785"/>
+  <autoFilter ref="A1:D850"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25152,7 +27511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -28342,12 +30701,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:36:51</t>
+          <t>2026-10-05 15:08:57</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>261002HHRWC6MC</t>
+          <t>261003ND0STEU0</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -28359,12 +30718,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:37:27</t>
+          <t>2026-10-05 15:09:57</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>261002JEPP9507</t>
+          <t>261004PYNMBJ77</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -28376,12 +30735,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:38:51</t>
+          <t>2026-10-05 15:10:26</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>261003ND0STEU0</t>
+          <t>261004Q63DF97T</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -28390,8 +30749,702 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:12:34</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>261004QGFRUB89</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:13:48</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>261004QT6B3W6T</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:15:10</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>261004QX1BTQAW</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:15:57</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>261004R2R0Q9HS</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:16:39</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>261004R3TD9APG</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:17:21</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>261005R7HD9X0E</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:18:10</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>261005R8GY74FG</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:18:49</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>261005RFNTFJ0M</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:19:28</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>261005RYAJ324R</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:21:07</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>261005S279WG28</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:21:50</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>261005S2KKTMH7</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:22:37</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>261005S3M1DU26</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:23:14</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>261005S561P3G2</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:25:45</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>261005S9MH5YJR</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:26:30</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>261005SAA9BT7C</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:27:31</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>261005SAJXUJYG</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:28:22</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>261005SB6KAGSA</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:29:17</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>261005SCWY7TRW</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:30:55</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>261005SEX8B805</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:31:37</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>261005SF9VA8TD</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32:19</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>261005SGFV6AYU</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33:28</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>261005SHVHRU6Q</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:34:48</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>261005SNEAWNNV</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:36:02</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>261005SNTUDA6S</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:37:04</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>261005SPK3PU2U</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:37:32</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>261005SRV913UH</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:38:02</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>261005SRV913UJ</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:38:50</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>261005SSG63N90</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:43:41</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>261005SKFS5G2H</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:46:48</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>261004QTYKSRBC</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:05:47</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:07:31</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>261004QA477QPM</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:08:11</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>261004QDHEFM8R</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:08:49</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>261004QKKKN7CP</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:09:55</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:10:33</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>261005S6S2BQR4</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:11:08</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>261005S7BW2KXG</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:11:49</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>261005S7DP9M25</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:12:29</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>261005SER9K7CC</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:23:23</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>261002HHRWC6MC</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:24:10</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>261004Q9QH1P3V</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:24:47</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>261002JEPP9507</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C190"/>
+  <autoFilter ref="A1:C232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
